--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6370,6 +6370,216 @@
         <v>12.30872821807861</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SE0000407991</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SVED-B.ST</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SVBDF</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SVEDBERGS GROUP B SK 1,25</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="G62" t="n">
+        <v>55</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>11.06708</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.969693902998803</v>
+      </c>
+      <c r="K62" t="n">
+        <v>301</v>
+      </c>
+      <c r="L62" t="n">
+        <v>10</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="N62" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>11.13849</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4.964766319312582</v>
+      </c>
+      <c r="R62" t="n">
+        <v>16645.3</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1494.394662113087</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4.472724512698923</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0.005454545454545379</v>
+      </c>
+      <c r="V62" t="n">
+        <v>-0.0009915265974929088</v>
+      </c>
+      <c r="W62" t="n">
+        <v>8</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0.5279636979103088</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>12.30872821807861</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0.4032482802867889</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>8.597104728221893</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="G63" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="J63" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="K63" t="n">
+        <v>121</v>
+      </c>
+      <c r="L63" t="n">
+        <v>12</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>45831.31329159903</v>
+      </c>
+      <c r="N63" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1715.78</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1491.527627920109</v>
+      </c>
+      <c r="T63" t="n">
+        <v>11.09400714981899</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>12</v>
+      </c>
+      <c r="X63" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>14.27337956428528</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -6420,7 +6420,7 @@
         <v>10</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="N62" t="n">
         <v>55.3</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="G63" t="n">
         <v>14.18</v>
@@ -6526,7 +6526,7 @@
         <v>12</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>45831.31329159903</v>
+        <v>45831.31329159722</v>
       </c>
       <c r="N63" t="n">
         <v>14.18</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD63"/>
+  <dimension ref="A1:AD67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6580,6 +6580,414 @@
         <v>14.27337956428528</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="G64" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>11.53806</v>
+      </c>
+      <c r="J64" t="n">
+        <v>7.839272806693673</v>
+      </c>
+      <c r="K64" t="n">
+        <v>160</v>
+      </c>
+      <c r="L64" t="n">
+        <v>9</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="N64" t="n">
+        <v>87.45</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>11.71124</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>7.46718537063539</v>
+      </c>
+      <c r="R64" t="n">
+        <v>13992</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1194.749659301662</v>
+      </c>
+      <c r="T64" t="n">
+        <v>7.055345526024306</v>
+      </c>
+      <c r="U64" t="n">
+        <v>-0.03316749585406298</v>
+      </c>
+      <c r="V64" t="n">
+        <v>-0.04746453468752498</v>
+      </c>
+      <c r="W64" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="X64" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0.5388140678405762</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>11.4948091506958</v>
+      </c>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="n">
+        <v>4.667</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="G65" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K65" t="n">
+        <v>34</v>
+      </c>
+      <c r="L65" t="n">
+        <v>9</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="N65" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1495.32</v>
+      </c>
+      <c r="T65" t="n">
+        <v>39.582</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.02757009345794392</v>
+      </c>
+      <c r="W65" t="n">
+        <v>-2.996</v>
+      </c>
+      <c r="X65" t="n">
+        <v>-0.3708006723881665</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.6616257429122925</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>13.05655670166016</v>
+      </c>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="n">
+        <v>-4.996</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="G66" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="J66" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="K66" t="n">
+        <v>162</v>
+      </c>
+      <c r="L66" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="N66" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6350.400000000001</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1489.057872633778</v>
+      </c>
+      <c r="T66" t="n">
+        <v>8.272543736854324</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="X66" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>12.85747975540161</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="G67" t="n">
+        <v>24528</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="J67" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="K67" t="n">
+        <v>101</v>
+      </c>
+      <c r="L67" t="n">
+        <v>11</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>45832.31308749835</v>
+      </c>
+      <c r="N67" t="n">
+        <v>24528</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2477328</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1204.761997393351</v>
+      </c>
+      <c r="T67" t="n">
+        <v>10.73550294706946</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>11</v>
+      </c>
+      <c r="X67" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>12.66160106658936</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -6626,7 +6626,7 @@
         <v>9</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="N64" t="n">
         <v>87.45</v>
@@ -6730,7 +6730,7 @@
         <v>9</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="N65" t="n">
         <v>43.98</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="G66" t="n">
         <v>39.2</v>
@@ -6830,7 +6830,7 @@
         <v>9.667</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="N66" t="n">
         <v>39.2</v>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="G67" t="n">
         <v>24528</v>
@@ -6934,7 +6934,7 @@
         <v>11</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>45832.31308749835</v>
+        <v>45832.3130875</v>
       </c>
       <c r="N67" t="n">
         <v>24528</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD67"/>
+  <dimension ref="A1:AD69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6988,6 +6988,212 @@
         <v>12.66160106658936</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="G68" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="K68" t="n">
+        <v>39</v>
+      </c>
+      <c r="L68" t="n">
+        <v>11</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="N68" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1421.55</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1421.55</v>
+      </c>
+      <c r="T68" t="n">
+        <v>34.92</v>
+      </c>
+      <c r="U68" t="n">
+        <v>-0.03315649867374004</v>
+      </c>
+      <c r="V68" t="n">
+        <v>-0.03315649867374004</v>
+      </c>
+      <c r="W68" t="n">
+        <v>8</v>
+      </c>
+      <c r="X68" t="n">
+        <v>-5.224298114719502</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0.4329348504543304</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>12.02781891822815</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0.4424935579299927</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>9.144985556602478</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="G69" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="K69" t="n">
+        <v>30</v>
+      </c>
+      <c r="L69" t="n">
+        <v>9</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>45833.31316271198</v>
+      </c>
+      <c r="N69" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1370.4</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1370.4</v>
+      </c>
+      <c r="T69" t="n">
+        <v>41.112</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>9</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>12.81225872039795</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -7034,7 +7034,7 @@
         <v>11</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="N68" t="n">
         <v>36.45</v>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="G69" t="n">
         <v>45.68</v>
@@ -7140,7 +7140,7 @@
         <v>9</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>45833.31316271198</v>
+        <v>45833.31316270833</v>
       </c>
       <c r="N69" t="n">
         <v>45.68</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD69"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7194,6 +7194,426 @@
         <v>12.81225872039795</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AU000000ALK9</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ALK.AX</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ALKEF</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ALKANE RESOURCES LTD.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1.77457</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.4085496768231177</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3664</v>
+      </c>
+      <c r="L70" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1.79458</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.3984219148770186</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2619.76</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1459.817896109396</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.3789069516795401</v>
+      </c>
+      <c r="U70" t="n">
+        <v>-0.01379310344827589</v>
+      </c>
+      <c r="V70" t="n">
+        <v>-0.02478954829888158</v>
+      </c>
+      <c r="W70" t="n">
+        <v>7</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.5076211094856262</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>11.50223774147034</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0.3658681511878967</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>6.871417284011841</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>45828.31201895834</v>
+      </c>
+      <c r="G71" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>9.04054</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.787444112851666</v>
+      </c>
+      <c r="K71" t="n">
+        <v>537</v>
+      </c>
+      <c r="L71" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="N71" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>9.205030000000001</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.732201850509993</v>
+      </c>
+      <c r="R71" t="n">
+        <v>13505.55</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1467.192393723866</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2.60614960154646</v>
+      </c>
+      <c r="U71" t="n">
+        <v>-0.001984126984126977</v>
+      </c>
+      <c r="V71" t="n">
+        <v>-0.01981824930120613</v>
+      </c>
+      <c r="W71" t="n">
+        <v>7</v>
+      </c>
+      <c r="X71" t="n">
+        <v>-17.4117981147195</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.5739187598228455</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>12.54904908370972</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0.44746994972229</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>8.103485465049744</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="G72" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="J72" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="K72" t="n">
+        <v>66</v>
+      </c>
+      <c r="L72" t="n">
+        <v>10</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="N72" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1752.96</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1494.573627548528</v>
+      </c>
+      <c r="T72" t="n">
+        <v>20.38054946657084</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>10</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>12.45218944549561</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="G73" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="J73" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="K73" t="n">
+        <v>214</v>
+      </c>
+      <c r="L73" t="n">
+        <v>9</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>45838.31344841498</v>
+      </c>
+      <c r="N73" t="n">
+        <v>8</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1712</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1459.651133147978</v>
+      </c>
+      <c r="T73" t="n">
+        <v>6.138719718846637</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>9</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>12.26600360870361</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -7244,7 +7244,7 @@
         <v>9.667</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="N70" t="n">
         <v>0.715</v>
@@ -7350,7 +7350,7 @@
         <v>9.667</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="N71" t="n">
         <v>25.15</v>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="G72" t="n">
         <v>26.56</v>
@@ -7456,7 +7456,7 @@
         <v>10</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="N72" t="n">
         <v>26.56</v>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="G73" t="n">
         <v>8</v>
@@ -7560,7 +7560,7 @@
         <v>9</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>45838.31344841498</v>
+        <v>45838.31344841435</v>
       </c>
       <c r="N73" t="n">
         <v>8</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD73"/>
+  <dimension ref="A1:AD76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7614,6 +7614,322 @@
         <v>12.26600360870361</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ZAE000015228</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HAR.JO</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HGMCF</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>HARMONY GOLD MNG   RC-,50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="G74" t="n">
+        <v>24528</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>2056.28</v>
+      </c>
+      <c r="J74" t="n">
+        <v>11.92833660785496</v>
+      </c>
+      <c r="K74" t="n">
+        <v>101</v>
+      </c>
+      <c r="L74" t="n">
+        <v>11</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="N74" t="n">
+        <v>25308</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>ZAc</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>2076.73</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>12.1864662233415</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2556108</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1230.833088557492</v>
+      </c>
+      <c r="T74" t="n">
+        <v>11.08504142195947</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.03180039138943247</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.02164003448029472</v>
+      </c>
+      <c r="W74" t="n">
+        <v>9</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.4939931035041809</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>12.66160106658936</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0.2714305818080902</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>7.414153695106506</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>US74767N1072</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>QSG</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>QUANTASING GRP  ADR/3CL.A</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6.820799687607375</v>
+      </c>
+      <c r="K75" t="n">
+        <v>214</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>8.016435304143554</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2022.3</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1715.517155086721</v>
+      </c>
+      <c r="T75" t="n">
+        <v>7.469653735294092</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.1812499999999999</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.1752925861037256</v>
+      </c>
+      <c r="W75" t="n">
+        <v>8</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-34.105101776716</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>36.3791764990048</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6086904406547546</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>12.26600360870361</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.3929778039455414</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>8.089129209518433</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="G76" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="J76" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="K76" t="n">
+        <v>16</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>45839.31381714748</v>
+      </c>
+      <c r="N76" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1759.52</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1492.600872629277</v>
+      </c>
+      <c r="T76" t="n">
+        <v>83.95879908539682</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="n">
+        <v>10</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>11.16087436676025</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -7664,7 +7664,7 @@
         <v>11</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="N74" t="n">
         <v>25308</v>
@@ -7770,7 +7770,7 @@
         <v>9</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="N75" t="n">
         <v>9.449999999999999</v>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="G76" t="n">
         <v>109.97</v>
@@ -7876,7 +7876,7 @@
         <v>10</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>45839.31381714748</v>
+        <v>45839.31381715278</v>
       </c>
       <c r="N76" t="n">
         <v>109.97</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD76"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7930,6 +7930,528 @@
         <v>11.16087436676025</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GB0000280353</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ALU.L</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>ALUMASC GRP PLC  LS -,125</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>45827.86588488426</v>
+      </c>
+      <c r="G77" t="n">
+        <v>367.666</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>0.85367</v>
+      </c>
+      <c r="J77" t="n">
+        <v>430.6886736092401</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="n">
+        <v>10</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>45847.66071417274</v>
+      </c>
+      <c r="N77" t="n">
+        <v>331.5</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0.86169</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>384.7091181283292</v>
+      </c>
+      <c r="R77" t="n">
+        <v>994.5</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1154.127354384988</v>
+      </c>
+      <c r="T77" t="n">
+        <v>401.0789257652164</v>
+      </c>
+      <c r="U77" t="n">
+        <v>-0.09836645216038464</v>
+      </c>
+      <c r="V77" t="n">
+        <v>-0.1067582184030864</v>
+      </c>
+      <c r="W77" t="n">
+        <v>8</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0.4649416506290436</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>11.58161377906799</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.3041629791259766</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>7.361870288848877</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>US4132163001</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>HARMONY GD MNG ADRRC,-50</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>45831.31329159722</v>
+      </c>
+      <c r="G78" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1.1503508</v>
+      </c>
+      <c r="J78" t="n">
+        <v>12.32667461090999</v>
+      </c>
+      <c r="K78" t="n">
+        <v>121</v>
+      </c>
+      <c r="L78" t="n">
+        <v>12</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>45847.66071417274</v>
+      </c>
+      <c r="N78" t="n">
+        <v>14.295</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1.1710973</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>12.20650068956695</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1729.695</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1476.986583437602</v>
+      </c>
+      <c r="T78" t="n">
+        <v>11.49473442571469</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.008110014104372398</v>
+      </c>
+      <c r="V78" t="n">
+        <v>-0.009749094961643223</v>
+      </c>
+      <c r="W78" t="n">
+        <v>10</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0.540931224822998</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>14.27337956428528</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.2210630774497986</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>7.607192039489746</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PLMURPL00190</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MUR.WA</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>MURAPOL S.A.        ZY 40</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>45832.3130875</v>
+      </c>
+      <c r="G79" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>4.26471</v>
+      </c>
+      <c r="J79" t="n">
+        <v>9.191715263171471</v>
+      </c>
+      <c r="K79" t="n">
+        <v>162</v>
+      </c>
+      <c r="L79" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>45847.66071417274</v>
+      </c>
+      <c r="N79" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>4.24323</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>9.261812345783754</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6366.599999999999</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1500.413600016968</v>
+      </c>
+      <c r="T79" t="n">
+        <v>8.495174269061048</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.002551020408163129</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.007626115540495748</v>
+      </c>
+      <c r="W79" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0.5925295352935791</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>12.85747975540161</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0.2532740533351898</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>6.015258733749389</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GRS393503008</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MYTIL.AT</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MYTHF</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>METLEN ENER.+MET. EO 0,97</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>45833.31316270833</v>
+      </c>
+      <c r="G80" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>45.68</v>
+      </c>
+      <c r="K80" t="n">
+        <v>30</v>
+      </c>
+      <c r="L80" t="n">
+        <v>9</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>45847.66071417274</v>
+      </c>
+      <c r="N80" t="n">
+        <v>47</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>47</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1410</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1410</v>
+      </c>
+      <c r="T80" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.02889667250437822</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.02889667250437822</v>
+      </c>
+      <c r="W80" t="n">
+        <v>8</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0.6434202790260315</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>12.81225872039795</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0.2901319563388824</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>6.935790419578552</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>45838.31344841435</v>
+      </c>
+      <c r="G81" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1.172883</v>
+      </c>
+      <c r="J81" t="n">
+        <v>22.64505496285648</v>
+      </c>
+      <c r="K81" t="n">
+        <v>66</v>
+      </c>
+      <c r="L81" t="n">
+        <v>10</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>45847.66071417274</v>
+      </c>
+      <c r="N81" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>1.1710973</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>23.26877536136408</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1798.5</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1535.739173850029</v>
+      </c>
+      <c r="T81" t="n">
+        <v>21.14091352304708</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.02597891566265065</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.02754333780733376</v>
+      </c>
+      <c r="W81" t="n">
+        <v>11</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.5395355224609375</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>12.45218944549561</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>0.2168360948562622</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>8.825953006744385</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -7976,7 +7976,7 @@
         <v>10</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>45847.66071417274</v>
+        <v>45847.66071417824</v>
       </c>
       <c r="N77" t="n">
         <v>331.5</v>
@@ -8082,7 +8082,7 @@
         <v>12</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>45847.66071417274</v>
+        <v>45847.66071417824</v>
       </c>
       <c r="N78" t="n">
         <v>14.295</v>
@@ -8184,7 +8184,7 @@
         <v>9.667</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>45847.66071417274</v>
+        <v>45847.66071417824</v>
       </c>
       <c r="N79" t="n">
         <v>39.3</v>
@@ -8290,7 +8290,7 @@
         <v>9</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>45847.66071417274</v>
+        <v>45847.66071417824</v>
       </c>
       <c r="N80" t="n">
         <v>47</v>
@@ -8396,7 +8396,7 @@
         <v>10</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>45847.66071417274</v>
+        <v>45847.66071417824</v>
       </c>
       <c r="N81" t="n">
         <v>27.25</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AD82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8452,6 +8452,112 @@
         <v>8.825953006744385</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>45839.31381715278</v>
+      </c>
+      <c r="G82" t="n">
+        <v>109.97</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1.1788282</v>
+      </c>
+      <c r="J82" t="n">
+        <v>93.2875545393298</v>
+      </c>
+      <c r="K82" t="n">
+        <v>16</v>
+      </c>
+      <c r="L82" t="n">
+        <v>10</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>45849.31404952101</v>
+      </c>
+      <c r="N82" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>1.1697274</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>97.15938944407048</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1818.4</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1554.550231105128</v>
+      </c>
+      <c r="T82" t="n">
+        <v>87.42299473051779</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0.03346367191052102</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.04150430273213268</v>
+      </c>
+      <c r="W82" t="n">
+        <v>10</v>
+      </c>
+      <c r="X82" t="n">
+        <v>-15.08960931013704</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.3977303088256807</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0.4318655133247375</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>11.16087436676025</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0.2254470139741898</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>7.882760763168335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -8502,7 +8502,7 @@
         <v>10</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>45849.31404952101</v>
+        <v>45849.31404952546</v>
       </c>
       <c r="N82" t="n">
         <v>113.65</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD82"/>
+  <dimension ref="A1:AD83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8558,6 +8558,110 @@
         <v>7.882760763168335</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CA86084H1001</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>RAY-A.TO</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>STGYF</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>STINGRAY GROUP INC.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>45856.31501794863</v>
+      </c>
+      <c r="G83" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1.59731</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6.686241243089944</v>
+      </c>
+      <c r="K83" t="n">
+        <v>223</v>
+      </c>
+      <c r="L83" t="n">
+        <v>11</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>45856.31501794863</v>
+      </c>
+      <c r="N83" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>1.59731</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>6.686241243089944</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2381.64</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1491.031797209058</v>
+      </c>
+      <c r="T83" t="n">
+        <v>6.01761711878095</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="n">
+        <v>11</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="n">
+        <v>0.2904720902442932</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>11.16241788864136</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0.2904720902442932</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>11.16241788864136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45856.31501794863</v>
+        <v>45856.31501795139</v>
       </c>
       <c r="G83" t="n">
         <v>10.68</v>
@@ -8608,7 +8608,7 @@
         <v>11</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>45856.31501794863</v>
+        <v>45856.31501795139</v>
       </c>
       <c r="N83" t="n">
         <v>10.68</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD83"/>
+  <dimension ref="A1:AD84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8662,6 +8662,110 @@
         <v>11.16241788864136</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MHY235921357</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>EUROSEAS LTD     DL -,01</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>45859.31868389084</v>
+      </c>
+      <c r="G84" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>1.1642799</v>
+      </c>
+      <c r="J84" t="n">
+        <v>42.44683774064983</v>
+      </c>
+      <c r="K84" t="n">
+        <v>35</v>
+      </c>
+      <c r="L84" t="n">
+        <v>11</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>45859.31868389084</v>
+      </c>
+      <c r="N84" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>1.1642799</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>42.44683774064983</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1729.7</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1485.639320922744</v>
+      </c>
+      <c r="T84" t="n">
+        <v>38.20215396658485</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="n">
+        <v>11</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="n">
+        <v>0.2958104014396667</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>11.3336226940155</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>0.2958104014396667</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>11.3336226940155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45859.31868389084</v>
+        <v>45859.31868388889</v>
       </c>
       <c r="G84" t="n">
         <v>49.42</v>
@@ -8712,7 +8712,7 @@
         <v>11</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>45859.31868389084</v>
+        <v>45859.31868388889</v>
       </c>
       <c r="N84" t="n">
         <v>49.42</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD84"/>
+  <dimension ref="A1:AD85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8766,6 +8766,110 @@
         <v>11.3336226940155</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NO0003080608</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SOFF.OL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SLOFF</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SOLSTAD OFFSHORE NK 1</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>45861.31586030619</v>
+      </c>
+      <c r="G85" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>11.81261</v>
+      </c>
+      <c r="J85" t="n">
+        <v>4.368213290712214</v>
+      </c>
+      <c r="K85" t="n">
+        <v>342</v>
+      </c>
+      <c r="L85" t="n">
+        <v>11</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>45861.31586030619</v>
+      </c>
+      <c r="N85" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>11.81261</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>4.368213290712214</v>
+      </c>
+      <c r="R85" t="n">
+        <v>17647.2</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1493.928945423577</v>
+      </c>
+      <c r="T85" t="n">
+        <v>3.931391961640993</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="n">
+        <v>11</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="n">
+        <v>0.3066190779209137</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>11.70399016141891</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0.3066190779209137</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>11.70399016141891</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45861.31586030619</v>
+        <v>45861.31586030093</v>
       </c>
       <c r="G85" t="n">
         <v>51.6</v>
@@ -8816,7 +8816,7 @@
         <v>11</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>45861.31586030619</v>
+        <v>45861.31586030093</v>
       </c>
       <c r="N85" t="n">
         <v>51.6</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD85"/>
+  <dimension ref="A1:AD86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8870,6 +8870,110 @@
         <v>11.70399016141891</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>45866.31676771137</v>
+      </c>
+      <c r="G86" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1.170686</v>
+      </c>
+      <c r="J86" t="n">
+        <v>24.76325846554926</v>
+      </c>
+      <c r="K86" t="n">
+        <v>60</v>
+      </c>
+      <c r="L86" t="n">
+        <v>11</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>45866.31676771137</v>
+      </c>
+      <c r="N86" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>1.170686</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>24.76325846554926</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1739.4</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1485.795507932956</v>
+      </c>
+      <c r="T86" t="n">
+        <v>22.28693261899434</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" t="n">
+        <v>11</v>
+      </c>
+      <c r="X86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="n">
+        <v>0.2712508141994476</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>11.0821453332901</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0.2712508141994476</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>11.0821453332901</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -8897,7 +8897,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45866.31676771137</v>
+        <v>45866.31676770833</v>
       </c>
       <c r="G86" t="n">
         <v>28.99</v>
@@ -8920,7 +8920,7 @@
         <v>11</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>45866.31676771137</v>
+        <v>45866.31676770833</v>
       </c>
       <c r="N86" t="n">
         <v>28.99</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD86"/>
+  <dimension ref="A1:AD87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8974,6 +8974,106 @@
         <v>11.0821453332901</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>45867.31623024277</v>
+      </c>
+      <c r="G87" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K87" t="n">
+        <v>37</v>
+      </c>
+      <c r="L87" t="n">
+        <v>11</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>45867.31623024277</v>
+      </c>
+      <c r="N87" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1487.4</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1487.4</v>
+      </c>
+      <c r="T87" t="n">
+        <v>36.18000000000001</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>11</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="n">
+        <v>0.2813227772712708</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>11.18139868974686</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.2813227772712708</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>11.18139868974686</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45867.31623024277</v>
+        <v>45867.31623024306</v>
       </c>
       <c r="G87" t="n">
         <v>40.2</v>
@@ -9020,7 +9020,7 @@
         <v>11</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>45867.31623024277</v>
+        <v>45867.31623024306</v>
       </c>
       <c r="N87" t="n">
         <v>40.2</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD87"/>
+  <dimension ref="A1:AD91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9074,6 +9074,420 @@
         <v>11.18139868974686</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CA86084H1001</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>RAY-A.TO</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>STGYF</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>STINGRAY GROUP INC.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>45856.31501795139</v>
+      </c>
+      <c r="G88" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>1.59731</v>
+      </c>
+      <c r="J88" t="n">
+        <v>6.686241243089944</v>
+      </c>
+      <c r="K88" t="n">
+        <v>223</v>
+      </c>
+      <c r="L88" t="n">
+        <v>11</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>45870.31741917298</v>
+      </c>
+      <c r="N88" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>1.58438</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>6.652444489327055</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2350.42</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1483.495121119933</v>
+      </c>
+      <c r="T88" t="n">
+        <v>6.378708606554792</v>
+      </c>
+      <c r="U88" t="n">
+        <v>-0.01310861423220977</v>
+      </c>
+      <c r="V88" t="n">
+        <v>-0.005054671606086192</v>
+      </c>
+      <c r="W88" t="n">
+        <v>7</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0.2904720902442932</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>11.16241788864136</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0.3154784440994263</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>7.545689761638641</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ROSNGNACNOR3</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SNG.RO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SOC.NA.DE GAZE NAT.ROMGAZ</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>45870.31741917298</v>
+      </c>
+      <c r="G89" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>RON</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>5.07464</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.590260589913767</v>
+      </c>
+      <c r="K89" t="n">
+        <v>941</v>
+      </c>
+      <c r="L89" t="n">
+        <v>9</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>45870.31741917298</v>
+      </c>
+      <c r="N89" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>RON</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>5.07464</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1.590260589913767</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7593.87</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1496.435215108855</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1.431234530922391</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>9</v>
+      </c>
+      <c r="X89" t="n">
+        <v>-1.884169022281021</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="n">
+        <v>0.3630712330341339</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>12.52227818965912</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0.3630712330341339</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>12.52227818965912</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>US10948W1036</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AAMI</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AAMI</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ACADIAN ASSET MAN.  -,001</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>45870.31741917298</v>
+      </c>
+      <c r="G90" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1.1427265</v>
+      </c>
+      <c r="J90" t="n">
+        <v>36.57043045733165</v>
+      </c>
+      <c r="K90" t="n">
+        <v>40</v>
+      </c>
+      <c r="L90" t="n">
+        <v>9</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>45870.31741917298</v>
+      </c>
+      <c r="N90" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>1.1427265</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>36.57043045733165</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1671.6</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1462.817218293266</v>
+      </c>
+      <c r="T90" t="n">
+        <v>32.91338741159849</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>9</v>
+      </c>
+      <c r="X90" t="n">
+        <v>-1.884169022281021</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="n">
+        <v>0.4482300877571106</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>11.64812421798706</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>0.4482300877571106</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>11.64812421798706</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>US1200761047</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BBW</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BBW</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>BUILD-A-BEAR WORK. DL-,01</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>45870.31741917298</v>
+      </c>
+      <c r="G91" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>1.1427265</v>
+      </c>
+      <c r="J91" t="n">
+        <v>44.37632276839646</v>
+      </c>
+      <c r="K91" t="n">
+        <v>24</v>
+      </c>
+      <c r="L91" t="n">
+        <v>9</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>45870.31741917298</v>
+      </c>
+      <c r="N91" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>1.1427265</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>44.37632276839646</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1217.04</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1065.031746441515</v>
+      </c>
+      <c r="T91" t="n">
+        <v>39.93869049155682</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" t="n">
+        <v>9</v>
+      </c>
+      <c r="X91" t="n">
+        <v>-1.884169022281021</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="n">
+        <v>0.4388217031955719</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>11.49081921577454</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0.4388217031955719</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>11.49081921577454</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -9124,7 +9124,7 @@
         <v>11</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>45870.31741917298</v>
+        <v>45870.31741917824</v>
       </c>
       <c r="N88" t="n">
         <v>10.54</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45870.31741917298</v>
+        <v>45870.31741917824</v>
       </c>
       <c r="G89" t="n">
         <v>8.07</v>
@@ -9226,7 +9226,7 @@
         <v>9</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>45870.31741917298</v>
+        <v>45870.31741917824</v>
       </c>
       <c r="N89" t="n">
         <v>8.07</v>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45870.31741917298</v>
+        <v>45870.31741917824</v>
       </c>
       <c r="G90" t="n">
         <v>41.79</v>
@@ -9330,7 +9330,7 @@
         <v>9</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>45870.31741917298</v>
+        <v>45870.31741917824</v>
       </c>
       <c r="N90" t="n">
         <v>41.79</v>
@@ -9411,7 +9411,7 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>45870.31741917298</v>
+        <v>45870.31741917824</v>
       </c>
       <c r="G91" t="n">
         <v>50.71</v>
@@ -9434,7 +9434,7 @@
         <v>9</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>45870.31741917298</v>
+        <v>45870.31741917824</v>
       </c>
       <c r="N91" t="n">
         <v>50.71</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD91"/>
+  <dimension ref="A1:AD93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9488,6 +9488,216 @@
         <v>11.49081921577454</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>US10948W1036</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AAMI</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AAMI</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ACADIAN ASSET MAN.  -,001</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>45870.31741917824</v>
+      </c>
+      <c r="G92" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1.1427265</v>
+      </c>
+      <c r="J92" t="n">
+        <v>36.57043045733165</v>
+      </c>
+      <c r="K92" t="n">
+        <v>40</v>
+      </c>
+      <c r="L92" t="n">
+        <v>9</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>45873.31921454846</v>
+      </c>
+      <c r="N92" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>1.1556685</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>34.24857560797062</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1583.2</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1369.943024318825</v>
+      </c>
+      <c r="T92" t="n">
+        <v>32.97732621406775</v>
+      </c>
+      <c r="U92" t="n">
+        <v>-0.0528834649437665</v>
+      </c>
+      <c r="V92" t="n">
+        <v>-0.06348995131654367</v>
+      </c>
+      <c r="W92" t="n">
+        <v>7</v>
+      </c>
+      <c r="X92" t="n">
+        <v>-1.884169022281021</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0.4482300877571106</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>11.64812421798706</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>0.4447803497314453</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>9.717224359512329</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>US88706T1088</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TIMB</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TIMB</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>TIM S.A.   SP.ADR/5</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>45873.31921454846</v>
+      </c>
+      <c r="G93" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>1.1556685</v>
+      </c>
+      <c r="J93" t="n">
+        <v>16.26764076376573</v>
+      </c>
+      <c r="K93" t="n">
+        <v>84</v>
+      </c>
+      <c r="L93" t="n">
+        <v>9</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>45873.31921454846</v>
+      </c>
+      <c r="N93" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>1.1556685</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>16.26764076376573</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1579.2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1366.481824156322</v>
+      </c>
+      <c r="T93" t="n">
+        <v>14.64087668738916</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>9</v>
+      </c>
+      <c r="X93" t="n">
+        <v>-25.10271751589134</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="n">
+        <v>0.3472197651863098</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>12.13259494304657</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>0.3472197651863098</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>12.13259494304657</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -9538,7 +9538,7 @@
         <v>9</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>45873.31921454846</v>
+        <v>45873.31921454861</v>
       </c>
       <c r="N92" t="n">
         <v>39.58</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45873.31921454846</v>
+        <v>45873.31921454861</v>
       </c>
       <c r="G93" t="n">
         <v>18.8</v>
@@ -9644,7 +9644,7 @@
         <v>9</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>45873.31921454846</v>
+        <v>45873.31921454861</v>
       </c>
       <c r="N93" t="n">
         <v>18.8</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD93"/>
+  <dimension ref="A1:AD95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9698,6 +9698,212 @@
         <v>12.13259494304657</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ROSNGNACNOR3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SNG.RO</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>SOC.NA.DE GAZE NAT.ROMGAZ</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>45870.31741917824</v>
+      </c>
+      <c r="G94" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>RON</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>5.07464</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1.590260589913767</v>
+      </c>
+      <c r="K94" t="n">
+        <v>941</v>
+      </c>
+      <c r="L94" t="n">
+        <v>9</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>45887.31475310019</v>
+      </c>
+      <c r="N94" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>RON</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>5.0611</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1.659718243069689</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7904.400000000001</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1561.794866728577</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1.526207605344296</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0.04089219330855021</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0.04367690024921478</v>
+      </c>
+      <c r="W94" t="n">
+        <v>6</v>
+      </c>
+      <c r="X94" t="n">
+        <v>-25.10271751589134</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0.3630712330341339</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>12.52227818965912</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0.2568554580211639</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>7.908601045608521</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>CA3803551074</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GSY.TO</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>EHMEF</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>GOEASY LTD</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>45887.31475310019</v>
+      </c>
+      <c r="G95" t="n">
+        <v>204.34</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1.61441</v>
+      </c>
+      <c r="J95" t="n">
+        <v>126.5725559182612</v>
+      </c>
+      <c r="K95" t="n">
+        <v>11</v>
+      </c>
+      <c r="L95" t="n">
+        <v>10</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>45887.31475310019</v>
+      </c>
+      <c r="N95" t="n">
+        <v>204.34</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>1.61441</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>126.5725559182612</v>
+      </c>
+      <c r="R95" t="n">
+        <v>2247.74</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1392.298115100873</v>
+      </c>
+      <c r="T95" t="n">
+        <v>113.9153003264351</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>10</v>
+      </c>
+      <c r="X95" t="n">
+        <v>-8.762804610960764</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="n">
+        <v>0.3689298629760742</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>12.58862376213074</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0.3689298629760742</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>12.58862376213074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -9744,7 +9744,7 @@
         <v>9</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>45887.31475310019</v>
+        <v>45887.31475310185</v>
       </c>
       <c r="N94" t="n">
         <v>8.4</v>
@@ -9827,7 +9827,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45887.31475310019</v>
+        <v>45887.31475310185</v>
       </c>
       <c r="G95" t="n">
         <v>204.34</v>
@@ -9850,7 +9850,7 @@
         <v>10</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>45887.31475310019</v>
+        <v>45887.31475310185</v>
       </c>
       <c r="N95" t="n">
         <v>204.34</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD95"/>
+  <dimension ref="A1:AD97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9904,6 +9904,216 @@
         <v>12.58862376213074</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>US1200761047</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BBW</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BBW</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>BUILD-A-BEAR WORK. DL-,01</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>45870.31741917824</v>
+      </c>
+      <c r="G96" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>1.1427265</v>
+      </c>
+      <c r="J96" t="n">
+        <v>44.37632276839646</v>
+      </c>
+      <c r="K96" t="n">
+        <v>24</v>
+      </c>
+      <c r="L96" t="n">
+        <v>9</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>45898.31134523222</v>
+      </c>
+      <c r="N96" t="n">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>1.1668612</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>57.42756722050575</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1608.24</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1378.261613292138</v>
+      </c>
+      <c r="T96" t="n">
+        <v>52.38897399643829</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0.321435614277263</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0.2941037841333713</v>
+      </c>
+      <c r="W96" t="n">
+        <v>8</v>
+      </c>
+      <c r="X96" t="n">
+        <v>-8.762804610960764</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>69.54466210169497</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0.4388217031955719</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>11.49081921577454</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0.3269346654415131</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>8.711905062198639</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CA8629521086</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SCR.TO</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>STHRF</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>STRATHCONA RES. LTD. NEW</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>45898.31134523222</v>
+      </c>
+      <c r="G97" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>1.60422</v>
+      </c>
+      <c r="J97" t="n">
+        <v>23.94310007355599</v>
+      </c>
+      <c r="K97" t="n">
+        <v>61</v>
+      </c>
+      <c r="L97" t="n">
+        <v>10</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>45898.31134523222</v>
+      </c>
+      <c r="N97" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>1.60422</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>23.94310007355599</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2343.01</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1460.529104486915</v>
+      </c>
+      <c r="T97" t="n">
+        <v>21.54879006620039</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>10</v>
+      </c>
+      <c r="X97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="n">
+        <v>0.4123817086219788</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>14.01883554458618</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>0.4123817086219788</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>14.01883554458618</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -9954,7 +9954,7 @@
         <v>9</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>45898.31134523222</v>
+        <v>45898.31134523148</v>
       </c>
       <c r="N96" t="n">
         <v>67.01000000000001</v>
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45898.31134523222</v>
+        <v>45898.31134523148</v>
       </c>
       <c r="G97" t="n">
         <v>38.41</v>
@@ -10060,7 +10060,7 @@
         <v>10</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>45898.31134523222</v>
+        <v>45898.31134523148</v>
       </c>
       <c r="N97" t="n">
         <v>38.41</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD97"/>
+  <dimension ref="A1:AD99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10114,6 +10114,212 @@
         <v>14.01883554458618</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NO0003080608</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SOFF.OL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SLOFF</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SOLSTAD OFFSHORE NK 1</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>45861.31586030093</v>
+      </c>
+      <c r="G98" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>11.81261</v>
+      </c>
+      <c r="J98" t="n">
+        <v>4.368213290712214</v>
+      </c>
+      <c r="K98" t="n">
+        <v>342</v>
+      </c>
+      <c r="L98" t="n">
+        <v>11</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>45908.3115973129</v>
+      </c>
+      <c r="N98" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>11.72931</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>4.910774802609873</v>
+      </c>
+      <c r="R98" t="n">
+        <v>19699.2</v>
+      </c>
+      <c r="S98" t="n">
+        <v>1679.484982492576</v>
+      </c>
+      <c r="T98" t="n">
+        <v>4.447825077998092</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0.1162790697674418</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0.1242067352918101</v>
+      </c>
+      <c r="W98" t="n">
+        <v>7</v>
+      </c>
+      <c r="X98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>46.3890092672498</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0.3066190779209137</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>11.70399016141891</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>0.3776753842830658</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>10.66755700111389</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>45908.3115973129</v>
+      </c>
+      <c r="G99" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>11.72931</v>
+      </c>
+      <c r="J99" t="n">
+        <v>8.393503113141353</v>
+      </c>
+      <c r="K99" t="n">
+        <v>178</v>
+      </c>
+      <c r="L99" t="n">
+        <v>10</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>45908.3115973129</v>
+      </c>
+      <c r="N99" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>11.72931</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>8.393503113141353</v>
+      </c>
+      <c r="R99" t="n">
+        <v>17524.1</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1494.043554139161</v>
+      </c>
+      <c r="T99" t="n">
+        <v>7.554152801827218</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>10</v>
+      </c>
+      <c r="X99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="n">
+        <v>0.3797236084938049</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>13.8728369474411</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0.3797236084938049</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>13.8728369474411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -10164,7 +10164,7 @@
         <v>11</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>45908.3115973129</v>
+        <v>45908.31159731482</v>
       </c>
       <c r="N98" t="n">
         <v>57.6</v>
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45908.3115973129</v>
+        <v>45908.31159731482</v>
       </c>
       <c r="G99" t="n">
         <v>98.45</v>
@@ -10266,7 +10266,7 @@
         <v>10</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>45908.3115973129</v>
+        <v>45908.31159731482</v>
       </c>
       <c r="N99" t="n">
         <v>98.45</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD99"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10320,6 +10320,212 @@
         <v>13.8728369474411</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NO0012851874</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>DOFG.OL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>DOF GROUP ASA  NK 2,50</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>45908.31159731482</v>
+      </c>
+      <c r="G100" t="n">
+        <v>98.45</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>11.72931</v>
+      </c>
+      <c r="J100" t="n">
+        <v>8.393503113141353</v>
+      </c>
+      <c r="K100" t="n">
+        <v>178</v>
+      </c>
+      <c r="L100" t="n">
+        <v>10</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>45916.3110381923</v>
+      </c>
+      <c r="N100" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>11.59146</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>8.264705222638046</v>
+      </c>
+      <c r="R100" t="n">
+        <v>17052.4</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1471.117529629572</v>
+      </c>
+      <c r="T100" t="n">
+        <v>7.678797427486633</v>
+      </c>
+      <c r="U100" t="n">
+        <v>-0.02691721686135096</v>
+      </c>
+      <c r="V100" t="n">
+        <v>-0.01534495058465557</v>
+      </c>
+      <c r="W100" t="n">
+        <v>8</v>
+      </c>
+      <c r="X100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0.3797236084938049</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>13.8728369474411</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0.2564534544944763</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>10.15930414199829</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BMG9156K1018</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2020.OL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>TTBKF</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2020 BULKERS LTD  DL 1</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>45916.3110381923</v>
+      </c>
+      <c r="G101" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>11.59146</v>
+      </c>
+      <c r="J101" t="n">
+        <v>12.5782256937435</v>
+      </c>
+      <c r="K101" t="n">
+        <v>119</v>
+      </c>
+      <c r="L101" t="n">
+        <v>9</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>45916.3110381923</v>
+      </c>
+      <c r="N101" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>11.59146</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>12.5782256937435</v>
+      </c>
+      <c r="R101" t="n">
+        <v>17350.2</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1496.808857555476</v>
+      </c>
+      <c r="T101" t="n">
+        <v>11.32040312436915</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>9</v>
+      </c>
+      <c r="X101" t="n">
+        <v>-5.731506127397168</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="n">
+        <v>0.4627172946929932</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>13.10245704650879</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>0.4627172946929932</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>13.10245704650879</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -10366,7 +10366,7 @@
         <v>10</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>45916.3110381923</v>
+        <v>45916.31103819444</v>
       </c>
       <c r="N100" t="n">
         <v>95.8</v>
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45916.3110381923</v>
+        <v>45916.31103819444</v>
       </c>
       <c r="G101" t="n">
         <v>145.8</v>
@@ -10472,7 +10472,7 @@
         <v>9</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>45916.3110381923</v>
+        <v>45916.31103819444</v>
       </c>
       <c r="N101" t="n">
         <v>145.8</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD101"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10526,6 +10526,216 @@
         <v>13.10245704650879</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CA8629521086</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SCR.TO</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>STHRF</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>STRATHCONA RES. LTD. NEW</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>45898.31134523148</v>
+      </c>
+      <c r="G102" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>1.60422</v>
+      </c>
+      <c r="J102" t="n">
+        <v>23.94310007355599</v>
+      </c>
+      <c r="K102" t="n">
+        <v>61</v>
+      </c>
+      <c r="L102" t="n">
+        <v>10</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>45919.31075569508</v>
+      </c>
+      <c r="N102" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>1.62545</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>22.54760220246701</v>
+      </c>
+      <c r="R102" t="n">
+        <v>2235.65</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1375.403734350488</v>
+      </c>
+      <c r="T102" t="n">
+        <v>21.71222375948847</v>
+      </c>
+      <c r="U102" t="n">
+        <v>-0.04582140067690699</v>
+      </c>
+      <c r="V102" t="n">
+        <v>-0.05828392592445641</v>
+      </c>
+      <c r="W102" t="n">
+        <v>8</v>
+      </c>
+      <c r="X102" t="n">
+        <v>-5.731506127397168</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0.4123817086219788</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>14.01883554458618</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0.33187335729599</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>11.14837050437927</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>45919.31075569508</v>
+      </c>
+      <c r="G103" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>9.156319999999999</v>
+      </c>
+      <c r="J103" t="n">
+        <v>3.326663987278732</v>
+      </c>
+      <c r="K103" t="n">
+        <v>447</v>
+      </c>
+      <c r="L103" t="n">
+        <v>9</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>45919.31075569508</v>
+      </c>
+      <c r="N103" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>9.156319999999999</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>3.326663987278732</v>
+      </c>
+      <c r="R103" t="n">
+        <v>13615.62</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1487.018802313593</v>
+      </c>
+      <c r="T103" t="n">
+        <v>2.993997588550859</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>9</v>
+      </c>
+      <c r="X103" t="n">
+        <v>-27.01284866150413</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="n">
+        <v>0.4532322883605957</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>13.78327178955078</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0.4532322883605957</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>13.78327178955078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -10576,7 +10576,7 @@
         <v>10</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>45919.31075569508</v>
+        <v>45919.31075569445</v>
       </c>
       <c r="N102" t="n">
         <v>36.65</v>
@@ -10659,7 +10659,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45919.31075569508</v>
+        <v>45919.31075569445</v>
       </c>
       <c r="G103" t="n">
         <v>30.46</v>
@@ -10682,7 +10682,7 @@
         <v>9</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>45919.31075569508</v>
+        <v>45919.31075569445</v>
       </c>
       <c r="N103" t="n">
         <v>30.46</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD103"/>
+  <dimension ref="A1:AD105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10736,6 +10736,216 @@
         <v>13.78327178955078</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>US88706T1088</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TIMB</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>TIMB</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>TIM S.A.   SP.ADR/5</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>45873.31921454861</v>
+      </c>
+      <c r="G104" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>1.1556685</v>
+      </c>
+      <c r="J104" t="n">
+        <v>16.26764076376573</v>
+      </c>
+      <c r="K104" t="n">
+        <v>84</v>
+      </c>
+      <c r="L104" t="n">
+        <v>9</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>45922.3121045092</v>
+      </c>
+      <c r="N104" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>1.1756407</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>18.47503238021617</v>
+      </c>
+      <c r="R104" t="n">
+        <v>1824.48</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1551.902719938158</v>
+      </c>
+      <c r="T104" t="n">
+        <v>16.6697238745703</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0.15531914893617</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0.1356921786327578</v>
+      </c>
+      <c r="W104" t="n">
+        <v>7</v>
+      </c>
+      <c r="X104" t="n">
+        <v>-27.01284866150413</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>19.34237528395504</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0.3472197651863098</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>12.13259494304657</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0.3393823802471161</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>10.20016956329346</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CY0200352116</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>FRONTLINE PLC        DL 1</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>45922.3121045092</v>
+      </c>
+      <c r="G105" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>1.1756407</v>
+      </c>
+      <c r="J105" t="n">
+        <v>19.74242640629913</v>
+      </c>
+      <c r="K105" t="n">
+        <v>75</v>
+      </c>
+      <c r="L105" t="n">
+        <v>10</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>45922.3121045092</v>
+      </c>
+      <c r="N105" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>1.1756407</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>19.74242640629913</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1740.75</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1480.681980472435</v>
+      </c>
+      <c r="T105" t="n">
+        <v>17.76818376566922</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>10</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="n">
+        <v>0.3464276492595673</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>13.14834642410278</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0.3464276492595673</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>13.14834642410278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -10786,7 +10786,7 @@
         <v>9</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>45922.3121045092</v>
+        <v>45922.31210451389</v>
       </c>
       <c r="N104" t="n">
         <v>21.72</v>
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45922.3121045092</v>
+        <v>45922.31210451389</v>
       </c>
       <c r="G105" t="n">
         <v>23.21</v>
@@ -10892,7 +10892,7 @@
         <v>10</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>45922.3121045092</v>
+        <v>45922.31210451389</v>
       </c>
       <c r="N105" t="n">
         <v>23.21</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD105"/>
+  <dimension ref="A1:AD107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10946,6 +10946,216 @@
         <v>13.14834642410278</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CA3803551074</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>GSY.TO</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EHMEF</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>GOEASY LTD</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>45887.31475310185</v>
+      </c>
+      <c r="G106" t="n">
+        <v>204.34</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>1.61441</v>
+      </c>
+      <c r="J106" t="n">
+        <v>126.5725559182612</v>
+      </c>
+      <c r="K106" t="n">
+        <v>11</v>
+      </c>
+      <c r="L106" t="n">
+        <v>10</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>45922.64671742354</v>
+      </c>
+      <c r="N106" t="n">
+        <v>186.51</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>1.62584</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>114.7160852236382</v>
+      </c>
+      <c r="R106" t="n">
+        <v>2051.61</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1261.876937460021</v>
+      </c>
+      <c r="T106" t="n">
+        <v>120.5515798127768</v>
+      </c>
+      <c r="U106" t="n">
+        <v>-0.08725653322893223</v>
+      </c>
+      <c r="V106" t="n">
+        <v>-0.09367331337039342</v>
+      </c>
+      <c r="W106" t="n">
+        <v>10</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0.3689298629760742</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>12.58862376213074</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0.35001140832901</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>12.43269777297974</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>US7194051022</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PLAB</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>plab</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PHOTRONICS INC.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>45922.64671742354</v>
+      </c>
+      <c r="G107" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>1.1775789</v>
+      </c>
+      <c r="J107" t="n">
+        <v>21.38285595980023</v>
+      </c>
+      <c r="K107" t="n">
+        <v>61</v>
+      </c>
+      <c r="L107" t="n">
+        <v>11</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>45922.64671742354</v>
+      </c>
+      <c r="N107" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>1.1775789</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>21.38285595980023</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1535.98</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1304.354213547814</v>
+      </c>
+      <c r="T107" t="n">
+        <v>19.24457036382021</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>11</v>
+      </c>
+      <c r="X107" t="n">
+        <v>-32.60529441021313</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="n">
+        <v>0.4009025096893311</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>12.89545369148254</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0.4009025096893311</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>12.89545369148254</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -10996,7 +10996,7 @@
         <v>10</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>45922.64671742354</v>
+        <v>45922.64671741898</v>
       </c>
       <c r="N106" t="n">
         <v>186.51</v>
@@ -11079,7 +11079,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>45922.64671742354</v>
+        <v>45922.64671741898</v>
       </c>
       <c r="G107" t="n">
         <v>25.18</v>
@@ -11102,7 +11102,7 @@
         <v>11</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>45922.64671742354</v>
+        <v>45922.64671741898</v>
       </c>
       <c r="N107" t="n">
         <v>25.18</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD107"/>
+  <dimension ref="A1:AD109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11156,6 +11156,216 @@
         <v>12.89545369148254</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BMG9156K1018</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2020.OL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>TTBKF</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2020 BULKERS LTD  DL 1</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>45916.31103819444</v>
+      </c>
+      <c r="G108" t="n">
+        <v>145.8</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>11.59146</v>
+      </c>
+      <c r="J108" t="n">
+        <v>12.5782256937435</v>
+      </c>
+      <c r="K108" t="n">
+        <v>119</v>
+      </c>
+      <c r="L108" t="n">
+        <v>9</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>45926.31078589206</v>
+      </c>
+      <c r="N108" t="n">
+        <v>150</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>11.71629</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>12.80268754016843</v>
+      </c>
+      <c r="R108" t="n">
+        <v>17850</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1523.519817280043</v>
+      </c>
+      <c r="T108" t="n">
+        <v>11.50288867587243</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0.0288065843621399</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0.01784527101756361</v>
+      </c>
+      <c r="W108" t="n">
+        <v>8</v>
+      </c>
+      <c r="X108" t="n">
+        <v>-32.60529441021313</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0.4627172946929932</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>13.10245704650879</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0.2328860610723495</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>8.610604822635651</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>JE00BLKGSR75</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>IDHC.L</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IDGXF</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>INTERGRATED DIA.H DL 0,25</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>45926.31078589206</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>1.1676786</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.4710200221191003</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3178</v>
+      </c>
+      <c r="L109" t="n">
+        <v>11</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>45926.31078589206</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>1.1676786</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.4710200221191003</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1747.9</v>
+      </c>
+      <c r="S109" t="n">
+        <v>1496.901630294501</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0.4239180199071903</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>11</v>
+      </c>
+      <c r="X109" t="n">
+        <v>-25.92755447907141</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="n">
+        <v>0.3778079152107239</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>12.47043168544769</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0.3778079152107239</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>12.47043168544769</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -11206,7 +11206,7 @@
         <v>9</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>45926.31078589206</v>
+        <v>45926.3107858912</v>
       </c>
       <c r="N108" t="n">
         <v>150</v>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45926.31078589206</v>
+        <v>45926.3107858912</v>
       </c>
       <c r="G109" t="n">
         <v>0.55</v>
@@ -11312,7 +11312,7 @@
         <v>11</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>45926.31078589206</v>
+        <v>45926.3107858912</v>
       </c>
       <c r="N109" t="n">
         <v>0.55</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD109"/>
+  <dimension ref="A1:AD111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11366,6 +11366,216 @@
         <v>12.47043168544769</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>US7194051022</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PLAB</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>plab</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PHOTRONICS INC.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>45922.64671741898</v>
+      </c>
+      <c r="G110" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>1.1775789</v>
+      </c>
+      <c r="J110" t="n">
+        <v>21.38285595980023</v>
+      </c>
+      <c r="K110" t="n">
+        <v>61</v>
+      </c>
+      <c r="L110" t="n">
+        <v>11</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>45930.31183867501</v>
+      </c>
+      <c r="N110" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>1.17495</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>19.60934507851398</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1405.44</v>
+      </c>
+      <c r="S110" t="n">
+        <v>1196.170049789353</v>
+      </c>
+      <c r="T110" t="n">
+        <v>19.31812901713809</v>
+      </c>
+      <c r="U110" t="n">
+        <v>-0.08498808578236694</v>
+      </c>
+      <c r="V110" t="n">
+        <v>-0.08294078604936828</v>
+      </c>
+      <c r="W110" t="n">
+        <v>9</v>
+      </c>
+      <c r="X110" t="n">
+        <v>-25.92755447907141</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0.4009025096893311</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>12.89545369148254</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0.2432376742362976</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>8.526162147521973</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>CNE1000004Q8</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>1171.HK</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>YZCHF</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>YANKUANG ENERGY GR.H YC 1</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>45930.31183867501</v>
+      </c>
+      <c r="G111" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>9.139860000000001</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.109426183770867</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L111" t="n">
+        <v>11</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>45930.31183867501</v>
+      </c>
+      <c r="N111" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>9.139860000000001</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1.109426183770867</v>
+      </c>
+      <c r="R111" t="n">
+        <v>11072.88</v>
+      </c>
+      <c r="S111" t="n">
+        <v>1211.493392677787</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0.9984835653937807</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>11</v>
+      </c>
+      <c r="X111" t="n">
+        <v>-52.97359541868677</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="n">
+        <v>0.1991575360298157</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>11.77479648590088</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0.1991575360298157</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>11.77479648590088</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -11416,7 +11416,7 @@
         <v>11</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>45930.31183867501</v>
+        <v>45930.31183868056</v>
       </c>
       <c r="N110" t="n">
         <v>23.04</v>
@@ -11499,7 +11499,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>45930.31183867501</v>
+        <v>45930.31183868056</v>
       </c>
       <c r="G111" t="n">
         <v>10.14</v>
@@ -11522,7 +11522,7 @@
         <v>11</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>45930.31183867501</v>
+        <v>45930.31183868056</v>
       </c>
       <c r="N111" t="n">
         <v>10.14</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD111"/>
+  <dimension ref="A1:AD113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11576,6 +11576,216 @@
         <v>11.77479648590088</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JE00BLKGSR75</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>IDHC.L</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>IDGXF</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>INTERGRATED DIA.H DL 0,25</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>45926.3107858912</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>1.1676786</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.4710200221191003</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3178</v>
+      </c>
+      <c r="L112" t="n">
+        <v>11</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>45931.60637917411</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>1.1756407</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.4465650091903079</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1668.45</v>
+      </c>
+      <c r="S112" t="n">
+        <v>1419.183599206799</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0.4470930089642148</v>
+      </c>
+      <c r="U112" t="n">
+        <v>-0.04545454545454553</v>
+      </c>
+      <c r="V112" t="n">
+        <v>-0.05191926410849856</v>
+      </c>
+      <c r="W112" t="n">
+        <v>9</v>
+      </c>
+      <c r="X112" t="n">
+        <v>-52.97359541868677</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0.3778079152107239</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>12.47043168544769</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0.2851734161376953</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>9.062057971954346</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GB00BZ3CNK81</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TRMD-A.CO</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>TORM PLC A         DL-,01</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>45931.60637917411</v>
+      </c>
+      <c r="G113" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>7.4663</v>
+      </c>
+      <c r="J113" t="n">
+        <v>18.14821263544192</v>
+      </c>
+      <c r="K113" t="n">
+        <v>77</v>
+      </c>
+      <c r="L113" t="n">
+        <v>9</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>45931.60637917411</v>
+      </c>
+      <c r="N113" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>7.4663</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>18.14821263544192</v>
+      </c>
+      <c r="R113" t="n">
+        <v>10433.5</v>
+      </c>
+      <c r="S113" t="n">
+        <v>1397.412372929028</v>
+      </c>
+      <c r="T113" t="n">
+        <v>16.33339137189773</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>9</v>
+      </c>
+      <c r="X113" t="n">
+        <v>-72.40310319061236</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="n">
+        <v>0.2742505669593811</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>11.06057590246201</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0.2742505669593811</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>11.06057590246201</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -11626,7 +11626,7 @@
         <v>11</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>45931.60637917411</v>
+        <v>45931.60637917824</v>
       </c>
       <c r="N112" t="n">
         <v>0.525</v>
@@ -11709,7 +11709,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45931.60637917411</v>
+        <v>45931.60637917824</v>
       </c>
       <c r="G113" t="n">
         <v>135.5</v>
@@ -11732,7 +11732,7 @@
         <v>9</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>45931.60637917411</v>
+        <v>45931.60637917824</v>
       </c>
       <c r="N113" t="n">
         <v>135.5</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD113"/>
+  <dimension ref="A1:AD115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11786,6 +11786,212 @@
         <v>11.06057590246201</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>45867.31623024306</v>
+      </c>
+      <c r="G114" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K114" t="n">
+        <v>37</v>
+      </c>
+      <c r="L114" t="n">
+        <v>11</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>45932.31030689038</v>
+      </c>
+      <c r="N114" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="R114" t="n">
+        <v>1705.7</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1705.7</v>
+      </c>
+      <c r="T114" t="n">
+        <v>42.70500000000001</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0.1467661691542288</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0.1467661691542288</v>
+      </c>
+      <c r="W114" t="n">
+        <v>11</v>
+      </c>
+      <c r="X114" t="n">
+        <v>-72.40310319061236</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0.2813227772712708</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>11.18139868974686</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0.1300459504127502</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>8.589673042297363</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>45919.31075569445</v>
+      </c>
+      <c r="G115" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>9.156319999999999</v>
+      </c>
+      <c r="J115" t="n">
+        <v>3.326663987278732</v>
+      </c>
+      <c r="K115" t="n">
+        <v>447</v>
+      </c>
+      <c r="L115" t="n">
+        <v>9</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>45932.31030689038</v>
+      </c>
+      <c r="N115" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>9.14071</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3.168244042311811</v>
+      </c>
+      <c r="R115" t="n">
+        <v>12945.12</v>
+      </c>
+      <c r="S115" t="n">
+        <v>1416.20508691338</v>
+      </c>
+      <c r="T115" t="n">
+        <v>3.021931357797944</v>
+      </c>
+      <c r="U115" t="n">
+        <v>-0.04924491135915954</v>
+      </c>
+      <c r="V115" t="n">
+        <v>-0.04762126429742342</v>
+      </c>
+      <c r="W115" t="n">
+        <v>3.667999999999999</v>
+      </c>
+      <c r="X115" t="n">
+        <v>-72.40310319061236</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0.4532322883605957</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>13.78327178955078</v>
+      </c>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="n">
+        <v>3.667999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -11832,7 +11832,7 @@
         <v>11</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>45932.31030689038</v>
+        <v>45932.31030688657</v>
       </c>
       <c r="N114" t="n">
         <v>46.1</v>
@@ -11938,7 +11938,7 @@
         <v>9</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>45932.31030689038</v>
+        <v>45932.31030688657</v>
       </c>
       <c r="N115" t="n">
         <v>28.96</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD115"/>
+  <dimension ref="A1:AD116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11992,6 +11992,112 @@
         <v>3.667999999999999</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>MHY235921357</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>EUROSEAS LTD     DL -,01</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>45859.31868388889</v>
+      </c>
+      <c r="G116" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>1.1642799</v>
+      </c>
+      <c r="J116" t="n">
+        <v>42.44683774064983</v>
+      </c>
+      <c r="K116" t="n">
+        <v>35</v>
+      </c>
+      <c r="L116" t="n">
+        <v>11</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>45932.77686049805</v>
+      </c>
+      <c r="N116" t="n">
+        <v>58.5429</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>1.172333</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>49.93709125308253</v>
+      </c>
+      <c r="R116" t="n">
+        <v>2049.0015</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1747.798193857889</v>
+      </c>
+      <c r="T116" t="n">
+        <v>50.02931206224352</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0.1845993524888709</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0.1764619913077659</v>
+      </c>
+      <c r="W116" t="n">
+        <v>11</v>
+      </c>
+      <c r="X116" t="n">
+        <v>-35.53153204066574</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>30.00818619312034</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0.2958104014396667</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>11.3336226940155</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0.2412175238132477</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>10.42466109991074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12042,7 +12042,7 @@
         <v>11</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>45932.77686049805</v>
+        <v>45932.77686049769</v>
       </c>
       <c r="N116" t="n">
         <v>58.5429</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD116"/>
+  <dimension ref="A1:AD117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12098,6 +12098,112 @@
         <v>10.42466109991074</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>MHY271836006</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>GSL</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>GLOBAL SHIP LEA. A DL-,01</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>45866.31676770833</v>
+      </c>
+      <c r="G117" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>1.170686</v>
+      </c>
+      <c r="J117" t="n">
+        <v>24.76325846554926</v>
+      </c>
+      <c r="K117" t="n">
+        <v>60</v>
+      </c>
+      <c r="L117" t="n">
+        <v>11</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>45937.7925605917</v>
+      </c>
+      <c r="N117" t="n">
+        <v>29.405</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>1.1660448</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>25.21772748354094</v>
+      </c>
+      <c r="R117" t="n">
+        <v>1764.3</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1513.063649012456</v>
+      </c>
+      <c r="T117" t="n">
+        <v>25.34445727349893</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.01431528113142466</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.01835255318373941</v>
+      </c>
+      <c r="W117" t="n">
+        <v>11</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>6.817035269875209</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.2712508141994476</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>11.0821453332901</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.1739733219146729</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>9.650276780128479</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12148,7 +12148,7 @@
         <v>11</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>45937.7925605917</v>
+        <v>45937.79256059028</v>
       </c>
       <c r="N117" t="n">
         <v>29.405</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD117"/>
+  <dimension ref="A1:AD118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12204,6 +12204,112 @@
         <v>9.650276780128479</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CY0200352116</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>FRONTLINE PLC        DL 1</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>45922.31210451389</v>
+      </c>
+      <c r="G118" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>1.1756407</v>
+      </c>
+      <c r="J118" t="n">
+        <v>19.74242640629913</v>
+      </c>
+      <c r="K118" t="n">
+        <v>75</v>
+      </c>
+      <c r="L118" t="n">
+        <v>10</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>45938.31060647314</v>
+      </c>
+      <c r="N118" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>1.1621151</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>18.87936917780347</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1645.5</v>
+      </c>
+      <c r="S118" t="n">
+        <v>1415.95268833526</v>
+      </c>
+      <c r="T118" t="n">
+        <v>18.47105181849349</v>
+      </c>
+      <c r="U118" t="n">
+        <v>-0.05471779405428689</v>
+      </c>
+      <c r="V118" t="n">
+        <v>-0.04371586403484273</v>
+      </c>
+      <c r="W118" t="n">
+        <v>8</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.3464276492595673</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>13.14834642410278</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.2134225070476532</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>9.038516879081726</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12254,7 +12254,7 @@
         <v>10</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>45938.31060647314</v>
+        <v>45938.31060646991</v>
       </c>
       <c r="N118" t="n">
         <v>21.94</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD118"/>
+  <dimension ref="A1:AD119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12310,6 +12310,110 @@
         <v>9.038516879081726</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>AU000000EHL7</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>EHL.AX</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>EOHDF</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>EMECO HOLDINGS LTD</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>45939.31124501226</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1.76536</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.7080708750623103</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2114</v>
+      </c>
+      <c r="L119" t="n">
+        <v>11</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>45939.31124501226</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>1.76536</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.7080708750623103</v>
+      </c>
+      <c r="R119" t="n">
+        <v>2642.5</v>
+      </c>
+      <c r="S119" t="n">
+        <v>1496.861829881724</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.6372637875560793</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>11</v>
+      </c>
+      <c r="X119" t="n">
+        <v>-16.18232303429361</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="n">
+        <v>0.2855813205242157</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>11.0721076130867</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.2855813205242157</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>11.0721076130867</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45939.31124501226</v>
+        <v>45939.31124501157</v>
       </c>
       <c r="G119" t="n">
         <v>1.25</v>
@@ -12360,7 +12360,7 @@
         <v>11</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>45939.31124501226</v>
+        <v>45939.31124501157</v>
       </c>
       <c r="N119" t="n">
         <v>1.25</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD119"/>
+  <dimension ref="A1:AD120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12414,6 +12414,110 @@
         <v>11.0721076130867</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>JE00BLKGSR75</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>IDHC.L</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>IDGXF</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>INTERGRATED DIA.H DL 0,25</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>45943.31223375205</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1.1614401</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.4184460309231616</v>
+      </c>
+      <c r="K120" t="n">
+        <v>3577</v>
+      </c>
+      <c r="L120" t="n">
+        <v>11</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>45943.31223375205</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>1.1614401</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.4184460309231616</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1738.422</v>
+      </c>
+      <c r="S120" t="n">
+        <v>1496.781452612149</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3766014278308455</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>11</v>
+      </c>
+      <c r="X120" t="n">
+        <v>-16.18232303429361</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="n">
+        <v>0.2966040074825287</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>11.19043534994125</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.2966040074825287</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>11.19043534994125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>45943.31223375205</v>
+        <v>45943.31223375</v>
       </c>
       <c r="G120" t="n">
         <v>0.486</v>
@@ -12464,7 +12464,7 @@
         <v>11</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>45943.31223375205</v>
+        <v>45943.31223375</v>
       </c>
       <c r="N120" t="n">
         <v>0.486</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD120"/>
+  <dimension ref="A1:AD121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12518,6 +12518,106 @@
         <v>11.19043534994125</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>45944.31177082711</v>
+      </c>
+      <c r="G121" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="K121" t="n">
+        <v>28</v>
+      </c>
+      <c r="L121" t="n">
+        <v>13</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>45944.31177082711</v>
+      </c>
+      <c r="N121" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1453.2</v>
+      </c>
+      <c r="S121" t="n">
+        <v>1453.2</v>
+      </c>
+      <c r="T121" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>13</v>
+      </c>
+      <c r="X121" t="n">
+        <v>-16.18232303429361</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="n">
+        <v>0.2024395316839218</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>11.76602411270142</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.2024395316839218</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>11.76602411270142</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12541,7 +12541,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>45944.31177082711</v>
+        <v>45944.31177082176</v>
       </c>
       <c r="G121" t="n">
         <v>51.9</v>
@@ -12564,7 +12564,7 @@
         <v>13</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>45944.31177082711</v>
+        <v>45944.31177082176</v>
       </c>
       <c r="N121" t="n">
         <v>51.9</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD121"/>
+  <dimension ref="A1:AD122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12618,6 +12618,110 @@
         <v>11.76602411270142</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>MHY235921357</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>EUROSEAS LTD     DL -,01</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>45945.31227497356</v>
+      </c>
+      <c r="G122" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>1.1634672</v>
+      </c>
+      <c r="J122" t="n">
+        <v>48.30389717905241</v>
+      </c>
+      <c r="K122" t="n">
+        <v>30</v>
+      </c>
+      <c r="L122" t="n">
+        <v>11</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>45945.31227497356</v>
+      </c>
+      <c r="N122" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>1.1634672</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>48.30389717905241</v>
+      </c>
+      <c r="R122" t="n">
+        <v>1686</v>
+      </c>
+      <c r="S122" t="n">
+        <v>1449.116915371572</v>
+      </c>
+      <c r="T122" t="n">
+        <v>43.47350746114717</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>11</v>
+      </c>
+      <c r="X122" t="n">
+        <v>-16.18232303429361</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="n">
+        <v>0.2790613770484924</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>11.09634882211685</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2790613770484924</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>11.09634882211685</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>45945.31227497356</v>
+        <v>45945.31227497685</v>
       </c>
       <c r="G122" t="n">
         <v>56.2</v>
@@ -12668,7 +12668,7 @@
         <v>11</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>45945.31227497356</v>
+        <v>45945.31227497685</v>
       </c>
       <c r="N122" t="n">
         <v>56.2</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD122"/>
+  <dimension ref="A1:AD123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12722,6 +12722,110 @@
         <v>11.09634882211685</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CY0200352116</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>FRONTLINE PLC        DL 1</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>45946.31157946614</v>
+      </c>
+      <c r="G123" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1.1652296</v>
+      </c>
+      <c r="J123" t="n">
+        <v>19.51546716629924</v>
+      </c>
+      <c r="K123" t="n">
+        <v>76</v>
+      </c>
+      <c r="L123" t="n">
+        <v>10</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>45946.31157946614</v>
+      </c>
+      <c r="N123" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>1.1652296</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>19.51546716629924</v>
+      </c>
+      <c r="R123" t="n">
+        <v>1728.24</v>
+      </c>
+      <c r="S123" t="n">
+        <v>1483.175504638742</v>
+      </c>
+      <c r="T123" t="n">
+        <v>17.56392044966932</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>10</v>
+      </c>
+      <c r="X123" t="n">
+        <v>-16.18232303429361</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="n">
+        <v>0.2530288696289062</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>11.63091194629669</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.2530288696289062</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>11.63091194629669</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>45946.31157946614</v>
+        <v>45946.31157946759</v>
       </c>
       <c r="G123" t="n">
         <v>22.74</v>
@@ -12772,7 +12772,7 @@
         <v>10</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>45946.31157946614</v>
+        <v>45946.31157946759</v>
       </c>
       <c r="N123" t="n">
         <v>22.74</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD123"/>
+  <dimension ref="A1:AD125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12826,6 +12826,216 @@
         <v>11.63091194629669</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GB00BZ3CNK81</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TRMD-A.CO</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>TORM PLC A         DL-,01</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>45931.60637917824</v>
+      </c>
+      <c r="G124" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>7.4663</v>
+      </c>
+      <c r="J124" t="n">
+        <v>18.14821263544192</v>
+      </c>
+      <c r="K124" t="n">
+        <v>77</v>
+      </c>
+      <c r="L124" t="n">
+        <v>9</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>45951.31190761607</v>
+      </c>
+      <c r="N124" t="n">
+        <v>133</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>7.4684</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>17.80836591505543</v>
+      </c>
+      <c r="R124" t="n">
+        <v>10241</v>
+      </c>
+      <c r="S124" t="n">
+        <v>1371.244175459268</v>
+      </c>
+      <c r="T124" t="n">
+        <v>16.93587270973963</v>
+      </c>
+      <c r="U124" t="n">
+        <v>-0.01845018450184499</v>
+      </c>
+      <c r="V124" t="n">
+        <v>-0.01872618131676473</v>
+      </c>
+      <c r="W124" t="n">
+        <v>6.334</v>
+      </c>
+      <c r="X124" t="n">
+        <v>-16.18232303429361</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.2742505669593811</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>11.06057590246201</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.2996828258037567</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>8.750004657745361</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GB00BG5NDX91</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SRB.L</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SRBIF</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>SERABI GOLD PLC  LS-,005</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>45951.31190761607</v>
+      </c>
+      <c r="G125" t="n">
+        <v>272</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0.86861</v>
+      </c>
+      <c r="J125" t="n">
+        <v>313.1439886715557</v>
+      </c>
+      <c r="K125" t="n">
+        <v>4</v>
+      </c>
+      <c r="L125" t="n">
+        <v>11</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>45951.31190761607</v>
+      </c>
+      <c r="N125" t="n">
+        <v>272</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0.86861</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>313.1439886715557</v>
+      </c>
+      <c r="R125" t="n">
+        <v>1088</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1252.575954686223</v>
+      </c>
+      <c r="T125" t="n">
+        <v>281.8295898044001</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>11</v>
+      </c>
+      <c r="X125" t="n">
+        <v>-22.72437240173347</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="n">
+        <v>0.3361083269119263</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>11.81242352724075</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3361083269119263</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>11.81242352724075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -12876,7 +12876,7 @@
         <v>9</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>45951.31190761607</v>
+        <v>45951.31190761574</v>
       </c>
       <c r="N124" t="n">
         <v>133</v>
@@ -12959,7 +12959,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>45951.31190761607</v>
+        <v>45951.31190761574</v>
       </c>
       <c r="G125" t="n">
         <v>272</v>
@@ -12982,7 +12982,7 @@
         <v>11</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>45951.31190761607</v>
+        <v>45951.31190761574</v>
       </c>
       <c r="N125" t="n">
         <v>272</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD125"/>
+  <dimension ref="A1:AD133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13036,6 +13036,842 @@
         <v>11.81242352724075</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CNE1000004Q8</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1171.HK</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>YZCHF</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>YANKUANG ENERGY GR.H YC 1</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>45930.31183868056</v>
+      </c>
+      <c r="G126" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>9.139860000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.109426183770867</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1092</v>
+      </c>
+      <c r="L126" t="n">
+        <v>11</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N126" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>9.014200000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1.206984535510639</v>
+      </c>
+      <c r="R126" t="n">
+        <v>11880.96</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1318.027112777618</v>
+      </c>
+      <c r="T126" t="n">
+        <v>1.138436983638694</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.07297830374753445</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.0879358655554503</v>
+      </c>
+      <c r="W126" t="n">
+        <v>8.334</v>
+      </c>
+      <c r="X126" t="n">
+        <v>-22.72437240173347</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>3.909057623224228</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.1991575360298157</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>11.77479648590088</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.3273219466209412</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>11.25605047607422</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>AU000000EHL7</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>EHL.AX</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>EOHDF</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>EMECO HOLDINGS LTD</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>45939.31124501157</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1.76536</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.7080708750623103</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2114</v>
+      </c>
+      <c r="L127" t="n">
+        <v>11</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>1.78393</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.6614609317630176</v>
+      </c>
+      <c r="R127" t="n">
+        <v>2494.52</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1398.328409747019</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.6399353807473308</v>
+      </c>
+      <c r="U127" t="n">
+        <v>-0.05600000000000005</v>
+      </c>
+      <c r="V127" t="n">
+        <v>-0.06582666360227152</v>
+      </c>
+      <c r="W127" t="n">
+        <v>8.334</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-22.72437240173347</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.2855813205242157</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>11.0721076130867</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375253438949585</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>9.874538311004638</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>DE000A0XYG76</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DR0.DE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>DT.ROHSTOFF AG NA O.N.</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>45944.31177082176</v>
+      </c>
+      <c r="G128" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="K128" t="n">
+        <v>28</v>
+      </c>
+      <c r="L128" t="n">
+        <v>13</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N128" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1414</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1414</v>
+      </c>
+      <c r="T128" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="U128" t="n">
+        <v>-0.02697495183044318</v>
+      </c>
+      <c r="V128" t="n">
+        <v>-0.02697495183044318</v>
+      </c>
+      <c r="W128" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="X128" t="n">
+        <v>-22.72437240173347</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.2024395316839218</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>11.76602411270142</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3300548195838928</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>11.19320572280884</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GB00BG5NDX91</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SRB.L</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>SRBIF</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SERABI GOLD PLC  LS-,005</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>45951.31190761574</v>
+      </c>
+      <c r="G129" t="n">
+        <v>272</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>0.86861</v>
+      </c>
+      <c r="J129" t="n">
+        <v>313.1439886715557</v>
+      </c>
+      <c r="K129" t="n">
+        <v>4</v>
+      </c>
+      <c r="L129" t="n">
+        <v>11</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N129" t="n">
+        <v>238.3</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>0.87074</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>273.6752647173669</v>
+      </c>
+      <c r="R129" t="n">
+        <v>953.2</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1094.701058869467</v>
+      </c>
+      <c r="T129" t="n">
+        <v>281.8295898044001</v>
+      </c>
+      <c r="U129" t="n">
+        <v>-0.1238970588235294</v>
+      </c>
+      <c r="V129" t="n">
+        <v>-0.126040177624441</v>
+      </c>
+      <c r="W129" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="X129" t="n">
+        <v>-22.72437240173347</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3361083269119263</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>11.81242352724075</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3526857495307922</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>11.40713573360443</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="G130" t="n">
+        <v>127.23</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>1.1604967</v>
+      </c>
+      <c r="J130" t="n">
+        <v>109.6340902994382</v>
+      </c>
+      <c r="K130" t="n">
+        <v>13</v>
+      </c>
+      <c r="L130" t="n">
+        <v>10</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N130" t="n">
+        <v>127.23</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>1.1604967</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>109.6340902994382</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1653.99</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1425.243173892696</v>
+      </c>
+      <c r="T130" t="n">
+        <v>98.67068126949435</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>10</v>
+      </c>
+      <c r="X130" t="n">
+        <v>-73.902078987865</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="n">
+        <v>0.2711050510406494</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>12.13359576463699</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.2711050510406494</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>12.13359576463699</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>US2540671011</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>DDS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>DDS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>DILLARDS A         DL-,01</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="G131" t="n">
+        <v>594.5700000000001</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>1.1604967</v>
+      </c>
+      <c r="J131" t="n">
+        <v>512.3409657261413</v>
+      </c>
+      <c r="K131" t="n">
+        <v>2</v>
+      </c>
+      <c r="L131" t="n">
+        <v>9</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N131" t="n">
+        <v>594.5700000000001</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>1.1604967</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>512.3409657261413</v>
+      </c>
+      <c r="R131" t="n">
+        <v>1189.14</v>
+      </c>
+      <c r="S131" t="n">
+        <v>1024.681931452283</v>
+      </c>
+      <c r="T131" t="n">
+        <v>461.1068691535272</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>9</v>
+      </c>
+      <c r="X131" t="n">
+        <v>-73.902078987865</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="n">
+        <v>0.326777458190918</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>11.84500670433044</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.326777458190918</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>11.84500670433044</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>JP3421100003</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1662.T</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>JPTXF</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>JAPAN PETROLEUM EXPLORAT.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1270</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>7.211811470755253</v>
+      </c>
+      <c r="K132" t="n">
+        <v>207</v>
+      </c>
+      <c r="L132" t="n">
+        <v>9</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1270</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>7.211811470755253</v>
+      </c>
+      <c r="R132" t="n">
+        <v>262890</v>
+      </c>
+      <c r="S132" t="n">
+        <v>1492.844974446337</v>
+      </c>
+      <c r="T132" t="n">
+        <v>6.490630323679728</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>9</v>
+      </c>
+      <c r="X132" t="n">
+        <v>-73.902078987865</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z132" t="inlineStr"/>
+      <c r="AA132" t="n">
+        <v>0.300293356180191</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>11.74045598506927</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.300293356180191</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>11.74045598506927</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GB00BG5NDX91</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SRB.L</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>SRBIF</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>SERABI GOLD PLC  LS-,005</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="G133" t="n">
+        <v>238.3</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>0.87074</v>
+      </c>
+      <c r="J133" t="n">
+        <v>273.6752647173669</v>
+      </c>
+      <c r="K133" t="n">
+        <v>5</v>
+      </c>
+      <c r="L133" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>45952.31202734319</v>
+      </c>
+      <c r="N133" t="n">
+        <v>238.3</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>0.87074</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>273.6752647173669</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1191.5</v>
+      </c>
+      <c r="S133" t="n">
+        <v>1368.376323586834</v>
+      </c>
+      <c r="T133" t="n">
+        <v>246.3077382456302</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-73.902078987865</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="n">
+        <v>0.3526857495307922</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>11.40713573360443</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3526857495307922</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>11.40713573360443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -13086,7 +13086,7 @@
         <v>11</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N126" t="n">
         <v>10.88</v>
@@ -13192,7 +13192,7 @@
         <v>11</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N127" t="n">
         <v>1.18</v>
@@ -13294,7 +13294,7 @@
         <v>13</v>
       </c>
       <c r="M128" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N128" t="n">
         <v>50.5</v>
@@ -13400,7 +13400,7 @@
         <v>11</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N129" t="n">
         <v>238.3</v>
@@ -13483,7 +13483,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="G130" t="n">
         <v>127.23</v>
@@ -13506,7 +13506,7 @@
         <v>10</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N130" t="n">
         <v>127.23</v>
@@ -13587,7 +13587,7 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="G131" t="n">
         <v>594.5700000000001</v>
@@ -13610,7 +13610,7 @@
         <v>9</v>
       </c>
       <c r="M131" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N131" t="n">
         <v>594.5700000000001</v>
@@ -13691,7 +13691,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="G132" t="n">
         <v>1270</v>
@@ -13714,7 +13714,7 @@
         <v>9</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N132" t="n">
         <v>1270</v>
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="G133" t="n">
         <v>238.3</v>
@@ -13818,7 +13818,7 @@
         <v>10.334</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>45952.31202734319</v>
+        <v>45952.31202733796</v>
       </c>
       <c r="N133" t="n">
         <v>238.3</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD133"/>
+  <dimension ref="A1:AD135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13872,6 +13872,216 @@
         <v>11.40713573360443</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>GB00BG5NDX91</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SRB.L</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SRBIF</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>SERABI GOLD PLC  LS-,005</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>45952.31202733796</v>
+      </c>
+      <c r="G134" t="n">
+        <v>238.3</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0.87074</v>
+      </c>
+      <c r="J134" t="n">
+        <v>273.6752647173669</v>
+      </c>
+      <c r="K134" t="n">
+        <v>5</v>
+      </c>
+      <c r="L134" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>45957.64629479435</v>
+      </c>
+      <c r="N134" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0.87327</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>264.6375118806326</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1155.5</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1323.187559403163</v>
+      </c>
+      <c r="T134" t="n">
+        <v>268.6821901434351</v>
+      </c>
+      <c r="U134" t="n">
+        <v>-0.03021401594628625</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.03302363787267315</v>
+      </c>
+      <c r="W134" t="n">
+        <v>11</v>
+      </c>
+      <c r="X134" t="n">
+        <v>-73.902078987865</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3526857495307922</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>11.40713573360443</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3673606514930725</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>12.30080962181091</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CNE1000004Q8</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>1171.HK</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>YZCHF</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>YANKUANG ENERGY GR.H YC 1</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>45957.64629479435</v>
+      </c>
+      <c r="G135" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>9.04006</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.203531834965697</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L135" t="n">
+        <v>11</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>45957.64629479435</v>
+      </c>
+      <c r="N135" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>9.04006</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>1.203531834965697</v>
+      </c>
+      <c r="R135" t="n">
+        <v>13523.84</v>
+      </c>
+      <c r="S135" t="n">
+        <v>1495.990070862362</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.083178651469128</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>11</v>
+      </c>
+      <c r="X135" t="n">
+        <v>-85.19927003378285</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="n">
+        <v>0.367568701505661</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>14.51498699188232</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.367568701505661</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>14.51498699188232</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -13922,7 +13922,7 @@
         <v>10.334</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>45957.64629479435</v>
+        <v>45957.64629479167</v>
       </c>
       <c r="N134" t="n">
         <v>231.1</v>
@@ -14005,7 +14005,7 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>45957.64629479435</v>
+        <v>45957.64629479167</v>
       </c>
       <c r="G135" t="n">
         <v>10.88</v>
@@ -14028,7 +14028,7 @@
         <v>11</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>45957.64629479435</v>
+        <v>45957.64629479167</v>
       </c>
       <c r="N135" t="n">
         <v>10.88</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD135"/>
+  <dimension ref="A1:AD137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14082,6 +14082,216 @@
         <v>14.51498699188232</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JE00BLKGSR75</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>IDHC.L</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>IDGXF</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>INTERGRATED DIA.H DL 0,25</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>45943.31223375</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1.1614401</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.4184460309231616</v>
+      </c>
+      <c r="K136" t="n">
+        <v>3577</v>
+      </c>
+      <c r="L136" t="n">
+        <v>11</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>45959.64861981657</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>1.1650938</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.4548989961151626</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1895.81</v>
+      </c>
+      <c r="S136" t="n">
+        <v>1627.173709103937</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.4563413660299487</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.09053497942386834</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.08711509369937076</v>
+      </c>
+      <c r="W136" t="n">
+        <v>11.667</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-85.19927003378285</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.2966040074825287</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>11.19043534994125</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2842162251472473</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>11.6882824344635</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SE0020050417</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>BOL.ST</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>BLIDF</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>BOLIDEN AB</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>45959.64861981657</v>
+      </c>
+      <c r="G137" t="n">
+        <v>436.9</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>10.89267</v>
+      </c>
+      <c r="J137" t="n">
+        <v>40.10954155409096</v>
+      </c>
+      <c r="K137" t="n">
+        <v>37</v>
+      </c>
+      <c r="L137" t="n">
+        <v>10</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>45959.64861981657</v>
+      </c>
+      <c r="N137" t="n">
+        <v>436.9</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>10.89267</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>40.10954155409096</v>
+      </c>
+      <c r="R137" t="n">
+        <v>16165.3</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1484.053037501365</v>
+      </c>
+      <c r="T137" t="n">
+        <v>36.09858739868186</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>10</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-52.60120591083598</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="n">
+        <v>0.4062377512454987</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>14.1412353515625</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.4062377512454987</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>14.1412353515625</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -14132,7 +14132,7 @@
         <v>11</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>45959.64861981657</v>
+        <v>45959.64861981481</v>
       </c>
       <c r="N136" t="n">
         <v>0.53</v>
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>45959.64861981657</v>
+        <v>45959.64861981481</v>
       </c>
       <c r="G137" t="n">
         <v>436.9</v>
@@ -14238,7 +14238,7 @@
         <v>10</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>45959.64861981657</v>
+        <v>45959.64861981481</v>
       </c>
       <c r="N137" t="n">
         <v>436.9</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD137"/>
+  <dimension ref="A1:AD139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14292,6 +14292,216 @@
         <v>14.1412353515625</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>US2540671011</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>DDS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DDS</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>DILLARDS A         DL-,01</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>45952.31202733796</v>
+      </c>
+      <c r="G138" t="n">
+        <v>594.5700000000001</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1.1604967</v>
+      </c>
+      <c r="J138" t="n">
+        <v>512.3409657261413</v>
+      </c>
+      <c r="K138" t="n">
+        <v>2</v>
+      </c>
+      <c r="L138" t="n">
+        <v>9</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>45964.31239458032</v>
+      </c>
+      <c r="N138" t="n">
+        <v>600.08</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>1.1538018</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>520.0893255670081</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1200.16</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1040.178651134016</v>
+      </c>
+      <c r="T138" t="n">
+        <v>482.0066238325153</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.009267201506971467</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.01512344387664766</v>
+      </c>
+      <c r="W138" t="n">
+        <v>7</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-52.60120591083598</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.326777458190918</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>11.84500670433044</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.3570038080215454</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>10.36695623397827</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DE0007100000</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>MBG.DE</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>MBGAF</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ GRP NA O.N.</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>45964.31239458032</v>
+      </c>
+      <c r="G139" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="K139" t="n">
+        <v>24</v>
+      </c>
+      <c r="L139" t="n">
+        <v>10</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>45964.31239458032</v>
+      </c>
+      <c r="N139" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1349.04</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1349.04</v>
+      </c>
+      <c r="T139" t="n">
+        <v>50.589</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>10</v>
+      </c>
+      <c r="X139" t="n">
+        <v>-48.72702599040259</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="n">
+        <v>0.3549001812934875</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>13.84887111186981</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3549001812934875</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>13.84887111186981</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -14342,7 +14342,7 @@
         <v>9</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>45964.31239458032</v>
+        <v>45964.31239458334</v>
       </c>
       <c r="N138" t="n">
         <v>600.08</v>
@@ -14425,7 +14425,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>45964.31239458032</v>
+        <v>45964.31239458334</v>
       </c>
       <c r="G139" t="n">
         <v>56.21</v>
@@ -14448,7 +14448,7 @@
         <v>10</v>
       </c>
       <c r="M139" s="2" t="n">
-        <v>45964.31239458032</v>
+        <v>45964.31239458334</v>
       </c>
       <c r="N139" t="n">
         <v>56.21</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD139"/>
+  <dimension ref="A1:AD145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14502,6 +14502,636 @@
         <v>13.84887111186981</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MHY235921357</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ESEA</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>EUROSEAS LTD     DL -,01</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>45945.31227497685</v>
+      </c>
+      <c r="G140" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>1.1634672</v>
+      </c>
+      <c r="J140" t="n">
+        <v>48.30389717905241</v>
+      </c>
+      <c r="K140" t="n">
+        <v>30</v>
+      </c>
+      <c r="L140" t="n">
+        <v>11</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="N140" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>1.1516757</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>51.35994447047897</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1774.5</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1540.798334114369</v>
+      </c>
+      <c r="T140" t="n">
+        <v>46.66888932539646</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.052491103202847</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.0632670958224848</v>
+      </c>
+      <c r="W140" t="n">
+        <v>9</v>
+      </c>
+      <c r="X140" t="n">
+        <v>-48.72702599040259</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.2790613770484924</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>11.09634882211685</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.2662166953086853</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>8.860348701477051</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PAP310761054</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>COPA HOLDINGS CL.A O.N.</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>45952.31202733796</v>
+      </c>
+      <c r="G141" t="n">
+        <v>127.23</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>1.1604967</v>
+      </c>
+      <c r="J141" t="n">
+        <v>109.6340902994382</v>
+      </c>
+      <c r="K141" t="n">
+        <v>13</v>
+      </c>
+      <c r="L141" t="n">
+        <v>10</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="N141" t="n">
+        <v>127.67</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>1.1516757</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>110.8558598570761</v>
+      </c>
+      <c r="R141" t="n">
+        <v>1659.71</v>
+      </c>
+      <c r="S141" t="n">
+        <v>1441.126178141989</v>
+      </c>
+      <c r="T141" t="n">
+        <v>100.1003712211106</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.003458303859152689</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.01114406617778241</v>
+      </c>
+      <c r="W141" t="n">
+        <v>8</v>
+      </c>
+      <c r="X141" t="n">
+        <v>-48.72702599040259</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.2711050510406494</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>12.13359576463699</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3303297162055969</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>11.09929978847504</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SE0020050417</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>BOL.ST</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BLIDF</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>BOLIDEN AB</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>45959.64861981481</v>
+      </c>
+      <c r="G142" t="n">
+        <v>436.9</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>10.89267</v>
+      </c>
+      <c r="J142" t="n">
+        <v>40.10954155409096</v>
+      </c>
+      <c r="K142" t="n">
+        <v>37</v>
+      </c>
+      <c r="L142" t="n">
+        <v>10</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="N142" t="n">
+        <v>412.1</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>10.96961</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>37.56742491300967</v>
+      </c>
+      <c r="R142" t="n">
+        <v>15247.7</v>
+      </c>
+      <c r="S142" t="n">
+        <v>1389.994721781358</v>
+      </c>
+      <c r="T142" t="n">
+        <v>36.09858739868186</v>
+      </c>
+      <c r="U142" t="n">
+        <v>-0.0567635614557106</v>
+      </c>
+      <c r="V142" t="n">
+        <v>-0.06337934921677013</v>
+      </c>
+      <c r="W142" t="n">
+        <v>8</v>
+      </c>
+      <c r="X142" t="n">
+        <v>-48.72702599040259</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.4062377512454987</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>14.1412353515625</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3947633504867554</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>12.00342774391174</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="G143" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>8.94941</v>
+      </c>
+      <c r="J143" t="n">
+        <v>3.439332872222862</v>
+      </c>
+      <c r="K143" t="n">
+        <v>435</v>
+      </c>
+      <c r="L143" t="n">
+        <v>10</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="N143" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>8.94941</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>3.439332872222862</v>
+      </c>
+      <c r="R143" t="n">
+        <v>13389.3</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1496.109799416945</v>
+      </c>
+      <c r="T143" t="n">
+        <v>3.095399585000576</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>10</v>
+      </c>
+      <c r="X143" t="n">
+        <v>-45.35049917238217</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="n">
+        <v>0.3477267026901245</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>13.11657953262329</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3477267026901245</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>13.11657953262329</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CA8629521086</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SCR.TO</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>STHRF</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>STRATHCONA RES. LTD. NEW</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="G144" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1.62267</v>
+      </c>
+      <c r="J144" t="n">
+        <v>22.68483425465437</v>
+      </c>
+      <c r="K144" t="n">
+        <v>65</v>
+      </c>
+      <c r="L144" t="n">
+        <v>10</v>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="N144" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>1.62267</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>22.68483425465437</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2392.65</v>
+      </c>
+      <c r="S144" t="n">
+        <v>1474.514226552534</v>
+      </c>
+      <c r="T144" t="n">
+        <v>20.41635082918893</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>10</v>
+      </c>
+      <c r="X144" t="n">
+        <v>-45.35049917238217</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="n">
+        <v>0.3056094646453857</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>12.78300178050995</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0.3056094646453857</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>12.78300178050995</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>US2338252073</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MBGYY</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>MBGYY</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ GRP ADR/1/4</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="G145" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>1.1516757</v>
+      </c>
+      <c r="J145" t="n">
+        <v>14.48324385067776</v>
+      </c>
+      <c r="K145" t="n">
+        <v>96</v>
+      </c>
+      <c r="L145" t="n">
+        <v>10</v>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>45967.31198451731</v>
+      </c>
+      <c r="N145" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>1.1516757</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>14.48324385067776</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1601.28</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1390.391409665065</v>
+      </c>
+      <c r="T145" t="n">
+        <v>13.03491946560998</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>10</v>
+      </c>
+      <c r="X145" t="n">
+        <v>-45.35049917238217</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="n">
+        <v>0.3036738038063049</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>12.72175204753876</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0.3036738038063049</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>12.72175204753876</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -14552,7 +14552,7 @@
         <v>11</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="N140" t="n">
         <v>59.15</v>
@@ -14658,7 +14658,7 @@
         <v>10</v>
       </c>
       <c r="M141" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="N141" t="n">
         <v>127.67</v>
@@ -14764,7 +14764,7 @@
         <v>10</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="N142" t="n">
         <v>412.1</v>
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="G143" t="n">
         <v>30.78</v>
@@ -14870,7 +14870,7 @@
         <v>10</v>
       </c>
       <c r="M143" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="N143" t="n">
         <v>30.78</v>
@@ -14951,7 +14951,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="G144" t="n">
         <v>36.81</v>
@@ -14974,7 +14974,7 @@
         <v>10</v>
       </c>
       <c r="M144" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="N144" t="n">
         <v>36.81</v>
@@ -15055,7 +15055,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="G145" t="n">
         <v>16.68</v>
@@ -15078,7 +15078,7 @@
         <v>10</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>45967.31198451731</v>
+        <v>45967.31198451389</v>
       </c>
       <c r="N145" t="n">
         <v>16.68</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD145"/>
+  <dimension ref="A1:AD149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15132,6 +15132,422 @@
         <v>12.72175204753876</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>JP3421100003</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>1662.T</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>JPTXF</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>JAPAN PETROLEUM EXPLORAT.</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>45952.31202733796</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1270</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>7.211811470755253</v>
+      </c>
+      <c r="K146" t="n">
+        <v>207</v>
+      </c>
+      <c r="L146" t="n">
+        <v>9</v>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>45968.31168320835</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1300</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>176.974</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>7.34571179947337</v>
+      </c>
+      <c r="R146" t="n">
+        <v>269100</v>
+      </c>
+      <c r="S146" t="n">
+        <v>1520.562342490987</v>
+      </c>
+      <c r="T146" t="n">
+        <v>6.818949406705245</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0.02362204724409445</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0.01856680936004751</v>
+      </c>
+      <c r="W146" t="n">
+        <v>6.334</v>
+      </c>
+      <c r="X146" t="n">
+        <v>-45.35049917238217</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0.300293356180191</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>11.74045598506927</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0.5431622266769409</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>12.4176296081543</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DE0007100000</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>MBG.DE</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>MBGAF</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ GRP NA O.N.</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>45964.31239458334</v>
+      </c>
+      <c r="G147" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="K147" t="n">
+        <v>24</v>
+      </c>
+      <c r="L147" t="n">
+        <v>10</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>45968.31168320835</v>
+      </c>
+      <c r="N147" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1396.56</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1396.56</v>
+      </c>
+      <c r="T147" t="n">
+        <v>52.785</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0.03522504892367895</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0.03522504892367895</v>
+      </c>
+      <c r="W147" t="n">
+        <v>8</v>
+      </c>
+      <c r="X147" t="n">
+        <v>-45.35049917238217</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0.3549001812934875</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>13.84887111186981</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0.3590099811553955</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>11.72679126262665</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CA14150G4007</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CJ.TO</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>CRLFF</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>CARDINAL ENERGY LTD</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>45968.31168320835</v>
+      </c>
+      <c r="G148" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1.62789</v>
+      </c>
+      <c r="J148" t="n">
+        <v>4.975766175847262</v>
+      </c>
+      <c r="K148" t="n">
+        <v>300</v>
+      </c>
+      <c r="L148" t="n">
+        <v>11</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>45968.31168320835</v>
+      </c>
+      <c r="N148" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>1.62789</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>4.975766175847262</v>
+      </c>
+      <c r="R148" t="n">
+        <v>2430</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1492.729852754179</v>
+      </c>
+      <c r="T148" t="n">
+        <v>4.478189558262536</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>11</v>
+      </c>
+      <c r="X148" t="n">
+        <v>-26.54115716121967</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="n">
+        <v>0.463020384311676</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>13.99727082252502</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>0.463020384311676</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>13.99727082252502</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>IT0005561441</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ESF.MI</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>EDIL SAN FELICE S.P.A. SB</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>45968.31168320835</v>
+      </c>
+      <c r="G149" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K149" t="n">
+        <v>257</v>
+      </c>
+      <c r="L149" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>45968.31168320835</v>
+      </c>
+      <c r="N149" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R149" t="n">
+        <v>1413.5</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1413.5</v>
+      </c>
+      <c r="T149" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="X149" t="n">
+        <v>-26.54115716121967</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="n">
+        <v>0.5306060314178467</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>13.37236518096924</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0.5306060314178467</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>13.37236518096924</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -15182,7 +15182,7 @@
         <v>9</v>
       </c>
       <c r="M146" s="2" t="n">
-        <v>45968.31168320835</v>
+        <v>45968.31168320602</v>
       </c>
       <c r="N146" t="n">
         <v>1300</v>
@@ -15288,7 +15288,7 @@
         <v>10</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>45968.31168320835</v>
+        <v>45968.31168320602</v>
       </c>
       <c r="N147" t="n">
         <v>58.19</v>
@@ -15371,7 +15371,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>45968.31168320835</v>
+        <v>45968.31168320602</v>
       </c>
       <c r="G148" t="n">
         <v>8.1</v>
@@ -15394,7 +15394,7 @@
         <v>11</v>
       </c>
       <c r="M148" s="2" t="n">
-        <v>45968.31168320835</v>
+        <v>45968.31168320602</v>
       </c>
       <c r="N148" t="n">
         <v>8.1</v>
@@ -15471,7 +15471,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>45968.31168320835</v>
+        <v>45968.31168320602</v>
       </c>
       <c r="G149" t="n">
         <v>5.5</v>
@@ -15494,7 +15494,7 @@
         <v>9.667</v>
       </c>
       <c r="M149" s="2" t="n">
-        <v>45968.31168320835</v>
+        <v>45968.31168320602</v>
       </c>
       <c r="N149" t="n">
         <v>5.5</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD149"/>
+  <dimension ref="A1:AD151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15548,6 +15548,212 @@
         <v>13.37236518096924</v>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>IT0005561441</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ESF.MI</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>EDIL SAN FELICE S.P.A. SB</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>45968.31168320602</v>
+      </c>
+      <c r="G150" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K150" t="n">
+        <v>257</v>
+      </c>
+      <c r="L150" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>45971.31219984405</v>
+      </c>
+      <c r="N150" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1413.5</v>
+      </c>
+      <c r="S150" t="n">
+        <v>1413.5</v>
+      </c>
+      <c r="T150" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="X150" t="n">
+        <v>-26.54115716121967</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0.5306060314178467</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>13.37236518096924</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0.5269356966018677</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>11.29429835510254</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>JP3421100003</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>1662.T</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>JPTXF</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>JAPAN PETROLEUM EXPLORAT.</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>45971.31219984405</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1346</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>178.095</v>
+      </c>
+      <c r="J151" t="n">
+        <v>7.557764114657908</v>
+      </c>
+      <c r="K151" t="n">
+        <v>186</v>
+      </c>
+      <c r="L151" t="n">
+        <v>9</v>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>45971.31219984405</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1346</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>178.095</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>7.557764114657908</v>
+      </c>
+      <c r="R151" t="n">
+        <v>250356</v>
+      </c>
+      <c r="S151" t="n">
+        <v>1405.744125326371</v>
+      </c>
+      <c r="T151" t="n">
+        <v>6.801987703192117</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>9</v>
+      </c>
+      <c r="X151" t="n">
+        <v>-26.54115716121967</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="n">
+        <v>0.5417881011962891</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>14.99343538284302</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0.5417881011962891</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>14.99343538284302</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -15594,7 +15594,7 @@
         <v>9.667</v>
       </c>
       <c r="M150" s="2" t="n">
-        <v>45971.31219984405</v>
+        <v>45971.31219984953</v>
       </c>
       <c r="N150" t="n">
         <v>5.5</v>
@@ -15677,7 +15677,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>45971.31219984405</v>
+        <v>45971.31219984953</v>
       </c>
       <c r="G151" t="n">
         <v>1346</v>
@@ -15700,7 +15700,7 @@
         <v>9</v>
       </c>
       <c r="M151" s="2" t="n">
-        <v>45971.31219984405</v>
+        <v>45971.31219984953</v>
       </c>
       <c r="N151" t="n">
         <v>1346</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD151"/>
+  <dimension ref="A1:AD153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15754,6 +15754,216 @@
         <v>14.99343538284302</v>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CA14150G4007</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>CJ.TO</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CRLFF</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>CARDINAL ENERGY LTD</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>45968.31168320602</v>
+      </c>
+      <c r="G152" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1.62789</v>
+      </c>
+      <c r="J152" t="n">
+        <v>4.975766175847262</v>
+      </c>
+      <c r="K152" t="n">
+        <v>300</v>
+      </c>
+      <c r="L152" t="n">
+        <v>11</v>
+      </c>
+      <c r="M152" s="2" t="n">
+        <v>45972.31283198418</v>
+      </c>
+      <c r="N152" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>1.62173</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>5.278313899354393</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2568</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1583.494169806318</v>
+      </c>
+      <c r="T152" t="n">
+        <v>4.766843216415423</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0.05679012345679024</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0.06080424859506461</v>
+      </c>
+      <c r="W152" t="n">
+        <v>8</v>
+      </c>
+      <c r="X152" t="n">
+        <v>-26.54115716121967</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0.463020384311676</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>13.99727082252502</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>0.4338068962097168</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>10.60004091262817</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SE0020050417</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>BOL.ST</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>BLIDF</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BOLIDEN AB</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>45972.31283198418</v>
+      </c>
+      <c r="G153" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>10.99719</v>
+      </c>
+      <c r="J153" t="n">
+        <v>38.60076983302098</v>
+      </c>
+      <c r="K153" t="n">
+        <v>38</v>
+      </c>
+      <c r="L153" t="n">
+        <v>9</v>
+      </c>
+      <c r="M153" s="2" t="n">
+        <v>45972.31283198418</v>
+      </c>
+      <c r="N153" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>10.99719</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>38.60076983302098</v>
+      </c>
+      <c r="R153" t="n">
+        <v>16131</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1466.829253654797</v>
+      </c>
+      <c r="T153" t="n">
+        <v>34.74069284971888</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>9</v>
+      </c>
+      <c r="X153" t="n">
+        <v>-3.850077898184828</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="n">
+        <v>0.4372789561748505</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>13.54962468147278</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0.4372789561748505</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>13.54962468147278</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -15804,7 +15804,7 @@
         <v>11</v>
       </c>
       <c r="M152" s="2" t="n">
-        <v>45972.31283198418</v>
+        <v>45972.31283197916</v>
       </c>
       <c r="N152" t="n">
         <v>8.56</v>
@@ -15887,7 +15887,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>45972.31283198418</v>
+        <v>45972.31283197916</v>
       </c>
       <c r="G153" t="n">
         <v>424.5</v>
@@ -15910,7 +15910,7 @@
         <v>9</v>
       </c>
       <c r="M153" s="2" t="n">
-        <v>45972.31283198418</v>
+        <v>45972.31283197916</v>
       </c>
       <c r="N153" t="n">
         <v>424.5</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD153"/>
+  <dimension ref="A1:AD157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15964,6 +15964,426 @@
         <v>13.54962468147278</v>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>KYG8187G1055</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>1308.HK</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SITIF</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>SITC INTL HLDG.REGS HD-10</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>45967.31198451389</v>
+      </c>
+      <c r="G154" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>8.94941</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3.439332872222862</v>
+      </c>
+      <c r="K154" t="n">
+        <v>435</v>
+      </c>
+      <c r="L154" t="n">
+        <v>10</v>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>45974.31266104965</v>
+      </c>
+      <c r="N154" t="n">
+        <v>30.64</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>9.007440000000001</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>3.401632428303713</v>
+      </c>
+      <c r="R154" t="n">
+        <v>13328.4</v>
+      </c>
+      <c r="S154" t="n">
+        <v>1479.710106312115</v>
+      </c>
+      <c r="T154" t="n">
+        <v>3.164916169783731</v>
+      </c>
+      <c r="U154" t="n">
+        <v>-0.004548408057180042</v>
+      </c>
+      <c r="V154" t="n">
+        <v>-0.0109615571739593</v>
+      </c>
+      <c r="W154" t="n">
+        <v>8</v>
+      </c>
+      <c r="X154" t="n">
+        <v>-3.850077898184828</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0.3477267026901245</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>13.11657953262329</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0.2814382016658783</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>10.01965999603271</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>JP3421100003</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>1662.T</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>JPTXF</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>JAPAN PETROLEUM EXPLORAT.</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>45971.31219984953</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1346</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>178.095</v>
+      </c>
+      <c r="J155" t="n">
+        <v>7.557764114657908</v>
+      </c>
+      <c r="K155" t="n">
+        <v>186</v>
+      </c>
+      <c r="L155" t="n">
+        <v>9</v>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>45974.31266104965</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1348</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>179.466</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>7.511172032585559</v>
+      </c>
+      <c r="R155" t="n">
+        <v>250728</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1397.077998060914</v>
+      </c>
+      <c r="T155" t="n">
+        <v>6.814039824502194</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0.001485884101040114</v>
+      </c>
+      <c r="V155" t="n">
+        <v>-0.006164797070338013</v>
+      </c>
+      <c r="W155" t="n">
+        <v>7</v>
+      </c>
+      <c r="X155" t="n">
+        <v>-3.850077898184828</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0.5417881011962891</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>14.99343538284302</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0.4815155565738678</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>12.22759127616882</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>JP3610600003</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>5105.T</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>TOTTF</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>TOYO TIRE CORP.</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>45974.31266104965</v>
+      </c>
+      <c r="G156" t="n">
+        <v>4381</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>179.466</v>
+      </c>
+      <c r="J156" t="n">
+        <v>24.41130910590307</v>
+      </c>
+      <c r="K156" t="n">
+        <v>61</v>
+      </c>
+      <c r="L156" t="n">
+        <v>9</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>45974.31266104965</v>
+      </c>
+      <c r="N156" t="n">
+        <v>4381</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>179.466</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>24.41130910590307</v>
+      </c>
+      <c r="R156" t="n">
+        <v>267241</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1489.089855460087</v>
+      </c>
+      <c r="T156" t="n">
+        <v>21.97017819531276</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>9</v>
+      </c>
+      <c r="X156" t="n">
+        <v>-10.11653299075649</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="n">
+        <v>0.4296288788318634</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>13.51423597335815</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0.4296288788318634</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>13.51423597335815</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>LU0633102719</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>1910.HK</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SMSOF</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>SAMSONITE GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>45974.31266104965</v>
+      </c>
+      <c r="G157" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>9.007440000000001</v>
+      </c>
+      <c r="J157" t="n">
+        <v>2.15599548817422</v>
+      </c>
+      <c r="K157" t="n">
+        <v>691</v>
+      </c>
+      <c r="L157" t="n">
+        <v>9</v>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>45974.31266104965</v>
+      </c>
+      <c r="N157" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>9.007440000000001</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>2.15599548817422</v>
+      </c>
+      <c r="R157" t="n">
+        <v>13419.22</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1489.792882328386</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.940395939356798</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>9</v>
+      </c>
+      <c r="X157" t="n">
+        <v>-10.11653299075649</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="n">
+        <v>0.4226439297199249</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>13.28499150276184</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0.4226439297199249</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>13.28499150276184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -16014,7 +16014,7 @@
         <v>10</v>
       </c>
       <c r="M154" s="2" t="n">
-        <v>45974.31266104965</v>
+        <v>45974.31266105324</v>
       </c>
       <c r="N154" t="n">
         <v>30.64</v>
@@ -16120,7 +16120,7 @@
         <v>9</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>45974.31266104965</v>
+        <v>45974.31266105324</v>
       </c>
       <c r="N155" t="n">
         <v>1348</v>
@@ -16203,7 +16203,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>45974.31266104965</v>
+        <v>45974.31266105324</v>
       </c>
       <c r="G156" t="n">
         <v>4381</v>
@@ -16226,7 +16226,7 @@
         <v>9</v>
       </c>
       <c r="M156" s="2" t="n">
-        <v>45974.31266104965</v>
+        <v>45974.31266105324</v>
       </c>
       <c r="N156" t="n">
         <v>4381</v>
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>45974.31266104965</v>
+        <v>45974.31266105324</v>
       </c>
       <c r="G157" t="n">
         <v>19.42</v>
@@ -16330,7 +16330,7 @@
         <v>9</v>
       </c>
       <c r="M157" s="2" t="n">
-        <v>45974.31266104965</v>
+        <v>45974.31266105324</v>
       </c>
       <c r="N157" t="n">
         <v>19.42</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD157"/>
+  <dimension ref="A1:AD158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16384,6 +16384,106 @@
         <v>13.28499150276184</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CNE1000004Q8</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>1171.HK</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>YZCHF</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>YANKUANG ENERGY GR.H YC 1</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>45957.64629479167</v>
+      </c>
+      <c r="G158" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>9.04006</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1.203531834965697</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1243</v>
+      </c>
+      <c r="L158" t="n">
+        <v>11</v>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>45982.31271504953</v>
+      </c>
+      <c r="N158" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>8.983779999999999</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>1.147623828722431</v>
+      </c>
+      <c r="R158" t="n">
+        <v>12815.33</v>
+      </c>
+      <c r="S158" t="n">
+        <v>1426.496419101982</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.181869980947633</v>
+      </c>
+      <c r="U158" t="n">
+        <v>-0.05238970588235292</v>
+      </c>
+      <c r="V158" t="n">
+        <v>-0.04645328409186589</v>
+      </c>
+      <c r="W158" t="inlineStr"/>
+      <c r="X158" t="n">
+        <v>-10.11653299075649</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0.367568701505661</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>14.51498699188232</v>
+      </c>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -16434,7 +16434,7 @@
         <v>11</v>
       </c>
       <c r="M158" s="2" t="n">
-        <v>45982.31271504953</v>
+        <v>45982.3127150463</v>
       </c>
       <c r="N158" t="n">
         <v>10.31</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD158"/>
+  <dimension ref="A1:AD159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16484,6 +16484,106 @@
       <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr"/>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CY0200352116</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>FRO</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>FRONTLINE PLC        DL 1</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>45946.31157946759</v>
+      </c>
+      <c r="G159" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>1.1652296</v>
+      </c>
+      <c r="J159" t="n">
+        <v>19.51546716629924</v>
+      </c>
+      <c r="K159" t="n">
+        <v>76</v>
+      </c>
+      <c r="L159" t="n">
+        <v>10</v>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>45989.72886163503</v>
+      </c>
+      <c r="N159" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>1.1599582</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>20.13865672056114</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1775.36</v>
+      </c>
+      <c r="S159" t="n">
+        <v>1530.537910762646</v>
+      </c>
+      <c r="T159" t="n">
+        <v>20.23457316048447</v>
+      </c>
+      <c r="U159" t="n">
+        <v>0.02726473175021993</v>
+      </c>
+      <c r="V159" t="n">
+        <v>0.03193310972017449</v>
+      </c>
+      <c r="W159" t="inlineStr"/>
+      <c r="X159" t="n">
+        <v>-27.48994593085139</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0.2530288696289062</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>11.63091194629669</v>
+      </c>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -16534,7 +16534,7 @@
         <v>10</v>
       </c>
       <c r="M159" s="2" t="n">
-        <v>45989.72886163503</v>
+        <v>45989.72886163194</v>
       </c>
       <c r="N159" t="n">
         <v>23.36</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD159"/>
+  <dimension ref="A1:AD160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16584,6 +16584,106 @@
       <c r="AC159" t="inlineStr"/>
       <c r="AD159" t="inlineStr"/>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CA8629521086</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SCR.TO</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>STHRF</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>STRATHCONA RES. LTD. NEW</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>45967.31198451389</v>
+      </c>
+      <c r="G160" t="n">
+        <v>36.81</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1.62267</v>
+      </c>
+      <c r="J160" t="n">
+        <v>22.68483425465437</v>
+      </c>
+      <c r="K160" t="n">
+        <v>65</v>
+      </c>
+      <c r="L160" t="n">
+        <v>10</v>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>46010.89513640583</v>
+      </c>
+      <c r="N160" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>1.61605</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>24.47325268401349</v>
+      </c>
+      <c r="R160" t="n">
+        <v>2570.75</v>
+      </c>
+      <c r="S160" t="n">
+        <v>1590.761424460877</v>
+      </c>
+      <c r="T160" t="n">
+        <v>24.75426652988903</v>
+      </c>
+      <c r="U160" t="n">
+        <v>0.07443629448519418</v>
+      </c>
+      <c r="V160" t="n">
+        <v>0.07883762381874937</v>
+      </c>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="n">
+        <v>-15.64934439987532</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>13.41245507721037</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0.3056094646453857</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>12.78300178050995</v>
+      </c>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -16634,7 +16634,7 @@
         <v>10</v>
       </c>
       <c r="M160" s="2" t="n">
-        <v>46010.89513640583</v>
+        <v>46010.89513640046</v>
       </c>
       <c r="N160" t="n">
         <v>39.55</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD160"/>
+  <dimension ref="A1:AD161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16684,6 +16684,110 @@
       <c r="AC160" t="inlineStr"/>
       <c r="AD160" t="inlineStr"/>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DE000PAH0038</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PAH3.DE</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>POAHF</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>PORSCHE AUTOM.HLDG VZO</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>46030.31625655676</v>
+      </c>
+      <c r="G161" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="K161" t="n">
+        <v>38</v>
+      </c>
+      <c r="L161" t="n">
+        <v>10</v>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>46030.31625655676</v>
+      </c>
+      <c r="N161" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1469.46</v>
+      </c>
+      <c r="S161" t="n">
+        <v>1469.46</v>
+      </c>
+      <c r="T161" t="n">
+        <v>34.803</v>
+      </c>
+      <c r="U161" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" t="n">
+        <v>10</v>
+      </c>
+      <c r="X161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="n">
+        <v>0.2519268095493317</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>11.82720732688904</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0.2519268095493317</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>11.82720732688904</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -16711,7 +16711,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>46030.31625655676</v>
+        <v>46030.3162565625</v>
       </c>
       <c r="G161" t="n">
         <v>38.67</v>
@@ -16734,7 +16734,7 @@
         <v>10</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>46030.31625655676</v>
+        <v>46030.3162565625</v>
       </c>
       <c r="N161" t="n">
         <v>38.67</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD161"/>
+  <dimension ref="A1:AD162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16788,6 +16788,112 @@
         <v>11.82720732688904</v>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DE000PAH0038</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>PAH3.DE</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>POAHF</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>PORSCHE AUTOM.HLDG VZO</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>46030.3162565625</v>
+      </c>
+      <c r="G162" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="K162" t="n">
+        <v>38</v>
+      </c>
+      <c r="L162" t="n">
+        <v>10</v>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>46034.3181683455</v>
+      </c>
+      <c r="N162" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="R162" t="n">
+        <v>1463.76</v>
+      </c>
+      <c r="S162" t="n">
+        <v>1463.76</v>
+      </c>
+      <c r="T162" t="n">
+        <v>35.28</v>
+      </c>
+      <c r="U162" t="n">
+        <v>-0.003878975950349028</v>
+      </c>
+      <c r="V162" t="n">
+        <v>-0.003878975950349028</v>
+      </c>
+      <c r="W162" t="n">
+        <v>7</v>
+      </c>
+      <c r="X162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0.2519268095493317</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>11.82720732688904</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0.2220757454633713</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>8.373417973518372</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -16838,7 +16838,7 @@
         <v>10</v>
       </c>
       <c r="M162" s="2" t="n">
-        <v>46034.3181683455</v>
+        <v>46034.31816834491</v>
       </c>
       <c r="N162" t="n">
         <v>38.52</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD162"/>
+  <dimension ref="A1:AD163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16894,6 +16894,110 @@
         <v>8.373417973518372</v>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>FR0000051070</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MAU.PA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>MRELF</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>MAUREL ET PROM INH.EO-,77</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>46048.31877522622</v>
+      </c>
+      <c r="G163" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="K163" t="n">
+        <v>236</v>
+      </c>
+      <c r="L163" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>46048.31877522622</v>
+      </c>
+      <c r="N163" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="R163" t="n">
+        <v>1496.24</v>
+      </c>
+      <c r="S163" t="n">
+        <v>1496.24</v>
+      </c>
+      <c r="T163" t="n">
+        <v>5.706</v>
+      </c>
+      <c r="U163" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="X163" t="n">
+        <v>-1.424999999999986</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="n">
+        <v>0.4323444068431854</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>11.98598069381714</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0.4323444068431854</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>11.98598069381714</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>46048.31877522622</v>
+        <v>46048.31877523148</v>
       </c>
       <c r="G163" t="n">
         <v>6.34</v>
@@ -16944,7 +16944,7 @@
         <v>9.667</v>
       </c>
       <c r="M163" s="2" t="n">
-        <v>46048.31877522622</v>
+        <v>46048.31877523148</v>
       </c>
       <c r="N163" t="n">
         <v>6.34</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD163"/>
+  <dimension ref="A1:AD169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16998,6 +16998,632 @@
         <v>11.98598069381714</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>US2338252073</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MBGYY</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>MBGYY</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>MERCEDES-BENZ GRP ADR/1/4</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>45967.31198451389</v>
+      </c>
+      <c r="G164" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>1.1516757</v>
+      </c>
+      <c r="J164" t="n">
+        <v>14.48324385067776</v>
+      </c>
+      <c r="K164" t="n">
+        <v>96</v>
+      </c>
+      <c r="L164" t="n">
+        <v>10</v>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="N164" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>14.2450998860392</v>
+      </c>
+      <c r="R164" t="n">
+        <v>1637.76</v>
+      </c>
+      <c r="S164" t="n">
+        <v>1367.529589059763</v>
+      </c>
+      <c r="T164" t="n">
+        <v>13.93130343482826</v>
+      </c>
+      <c r="U164" t="n">
+        <v>0.02278177458033559</v>
+      </c>
+      <c r="V164" t="n">
+        <v>-0.01644272285227111</v>
+      </c>
+      <c r="W164" t="n">
+        <v>-2.996</v>
+      </c>
+      <c r="X164" t="n">
+        <v>-1.424999999999986</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0.3036738038063049</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>12.72175204753876</v>
+      </c>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="n">
+        <v>-4.996</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>JP3610600003</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>5105.T</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>TOTTF</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>TOYO TIRE CORP.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>45974.31266105324</v>
+      </c>
+      <c r="G165" t="n">
+        <v>4381</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>179.466</v>
+      </c>
+      <c r="J165" t="n">
+        <v>24.41130910590307</v>
+      </c>
+      <c r="K165" t="n">
+        <v>61</v>
+      </c>
+      <c r="L165" t="n">
+        <v>9</v>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="N165" t="n">
+        <v>4132</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>183.589</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>22.50679506942137</v>
+      </c>
+      <c r="R165" t="n">
+        <v>252052</v>
+      </c>
+      <c r="S165" t="n">
+        <v>1372.914499234704</v>
+      </c>
+      <c r="T165" t="n">
+        <v>22.26410359913158</v>
+      </c>
+      <c r="U165" t="n">
+        <v>-0.05683633873544858</v>
+      </c>
+      <c r="V165" t="n">
+        <v>-0.07801769369349998</v>
+      </c>
+      <c r="W165" t="n">
+        <v>6</v>
+      </c>
+      <c r="X165" t="n">
+        <v>-1.424999999999986</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>0.4296288788318634</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>13.51423597335815</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>0.4283945262432098</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>10.65069055557251</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>BMG3922B1072</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>GENPACT LTD    DL 0,01</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="G166" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="J166" t="n">
+        <v>37.39129970086961</v>
+      </c>
+      <c r="K166" t="n">
+        <v>40</v>
+      </c>
+      <c r="L166" t="n">
+        <v>9</v>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="N166" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>37.39129970086961</v>
+      </c>
+      <c r="R166" t="n">
+        <v>1791.2</v>
+      </c>
+      <c r="S166" t="n">
+        <v>1495.651988034784</v>
+      </c>
+      <c r="T166" t="n">
+        <v>33.65216973078265</v>
+      </c>
+      <c r="U166" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>9</v>
+      </c>
+      <c r="X166" t="n">
+        <v>-36.18429420767126</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="n">
+        <v>0.5109041333198547</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>14.70826506614685</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0.5109041333198547</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>14.70826506614685</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>US80007P8692</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>SANDRIDGE ENERGY  DL-,001</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="G167" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="J167" t="n">
+        <v>12.94249989646</v>
+      </c>
+      <c r="K167" t="n">
+        <v>115</v>
+      </c>
+      <c r="L167" t="n">
+        <v>12</v>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="N167" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>12.94249989646</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1782.5</v>
+      </c>
+      <c r="S167" t="n">
+        <v>1488.3874880929</v>
+      </c>
+      <c r="T167" t="n">
+        <v>11.648249906814</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>12</v>
+      </c>
+      <c r="X167" t="n">
+        <v>-36.18429420767126</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="n">
+        <v>0.4404408931732178</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>14.46690368652344</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0.4404408931732178</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>14.46690368652344</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>US01973R1014</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>ALSN</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ALSN</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>ALLISON TRANSM.HLDGS DL-1</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="G168" t="n">
+        <v>110.59</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="J168" t="n">
+        <v>92.34264926125881</v>
+      </c>
+      <c r="K168" t="n">
+        <v>16</v>
+      </c>
+      <c r="L168" t="n">
+        <v>10</v>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="N168" t="n">
+        <v>110.59</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>92.34264926125881</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1769.44</v>
+      </c>
+      <c r="S168" t="n">
+        <v>1477.482388180141</v>
+      </c>
+      <c r="T168" t="n">
+        <v>83.10838433513294</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" t="n">
+        <v>10</v>
+      </c>
+      <c r="X168" t="n">
+        <v>-36.18429420767126</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="n">
+        <v>0.4109965860843658</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>14.16379523277283</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>0.4109965860843658</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>14.16379523277283</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BMG7496G1033</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>RNR</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>RNR</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>RENAISSANCERE HLDGS  DL 1</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="G169" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="J169" t="n">
+        <v>229.958998160328</v>
+      </c>
+      <c r="K169" t="n">
+        <v>5</v>
+      </c>
+      <c r="L169" t="n">
+        <v>9</v>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>46051.32973271931</v>
+      </c>
+      <c r="N169" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>229.958998160328</v>
+      </c>
+      <c r="R169" t="n">
+        <v>1377</v>
+      </c>
+      <c r="S169" t="n">
+        <v>1149.79499080164</v>
+      </c>
+      <c r="T169" t="n">
+        <v>206.9630983442952</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>9</v>
+      </c>
+      <c r="X169" t="n">
+        <v>-36.18429420767126</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="n">
+        <v>0.4166250228881836</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>13.62182998657227</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>0.4166250228881836</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>13.62182998657227</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD169"/>
+  <dimension ref="A1:AD173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17048,7 +17048,7 @@
         <v>10</v>
       </c>
       <c r="M164" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="N164" t="n">
         <v>17.06</v>
@@ -17152,7 +17152,7 @@
         <v>9</v>
       </c>
       <c r="M165" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="N165" t="n">
         <v>4132</v>
@@ -17235,7 +17235,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="G166" t="n">
         <v>44.78</v>
@@ -17258,7 +17258,7 @@
         <v>9</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="N166" t="n">
         <v>44.78</v>
@@ -17339,7 +17339,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="G167" t="n">
         <v>15.5</v>
@@ -17362,7 +17362,7 @@
         <v>12</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="N167" t="n">
         <v>15.5</v>
@@ -17443,7 +17443,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="G168" t="n">
         <v>110.59</v>
@@ -17466,7 +17466,7 @@
         <v>10</v>
       </c>
       <c r="M168" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="N168" t="n">
         <v>110.59</v>
@@ -17547,7 +17547,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="G169" t="n">
         <v>275.4</v>
@@ -17570,7 +17570,7 @@
         <v>9</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>46051.32973271931</v>
+        <v>46051.32973271991</v>
       </c>
       <c r="N169" t="n">
         <v>275.4</v>
@@ -17622,6 +17622,426 @@
       </c>
       <c r="AD169" t="n">
         <v>13.62182998657227</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>LU0633102719</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>1910.HK</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SMSOF</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>SAMSONITE GROUP S.A.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>45974.31266105324</v>
+      </c>
+      <c r="G170" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>9.007440000000001</v>
+      </c>
+      <c r="J170" t="n">
+        <v>2.15599548817422</v>
+      </c>
+      <c r="K170" t="n">
+        <v>691</v>
+      </c>
+      <c r="L170" t="n">
+        <v>9</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>46052.32911183846</v>
+      </c>
+      <c r="N170" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>9.3161</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>2.116765599338779</v>
+      </c>
+      <c r="R170" t="n">
+        <v>13626.52</v>
+      </c>
+      <c r="S170" t="n">
+        <v>1462.685029143096</v>
+      </c>
+      <c r="T170" t="n">
+        <v>2.123111966451539</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0.01544799176107081</v>
+      </c>
+      <c r="V170" t="n">
+        <v>-0.01819571935591702</v>
+      </c>
+      <c r="W170" t="n">
+        <v>9</v>
+      </c>
+      <c r="X170" t="n">
+        <v>-36.18429420767126</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>0.4226439297199249</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>13.28499150276184</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>0.4621981382369995</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>13.98090171813965</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BMG7496G1033</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>RNR</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>RNR</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>RENAISSANCERE HLDGS  DL 1</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>46051.32973271991</v>
+      </c>
+      <c r="G171" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="J171" t="n">
+        <v>229.958998160328</v>
+      </c>
+      <c r="K171" t="n">
+        <v>5</v>
+      </c>
+      <c r="L171" t="n">
+        <v>9</v>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>46052.32911183846</v>
+      </c>
+      <c r="N171" t="n">
+        <v>282.72</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>1.1937448</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>236.8345395096172</v>
+      </c>
+      <c r="R171" t="n">
+        <v>1413.6</v>
+      </c>
+      <c r="S171" t="n">
+        <v>1184.172697548086</v>
+      </c>
+      <c r="T171" t="n">
+        <v>206.9630983442952</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0.02657952069716796</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0.0298989880991547</v>
+      </c>
+      <c r="W171" t="n">
+        <v>7</v>
+      </c>
+      <c r="X171" t="n">
+        <v>-36.18429420767126</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>0.4166250228881836</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>13.62182998657227</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>0.4391768574714661</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>11.86868786811829</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>JE00BLKGSR75</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>IDHC.L</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>IDGXF</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>INTERGRATED DIA.H DL 0,25</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>46052.32911183846</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>1.1937448</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0.498431490549739</v>
+      </c>
+      <c r="K172" t="n">
+        <v>3003</v>
+      </c>
+      <c r="L172" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>46052.32911183846</v>
+      </c>
+      <c r="N172" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>1.1937448</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>0.498431490549739</v>
+      </c>
+      <c r="R172" t="n">
+        <v>1786.785</v>
+      </c>
+      <c r="S172" t="n">
+        <v>1496.789766120866</v>
+      </c>
+      <c r="T172" t="n">
+        <v>0.4485883414947651</v>
+      </c>
+      <c r="U172" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="X172" t="n">
+        <v>-34.36683081738223</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z172" t="inlineStr"/>
+      <c r="AA172" t="n">
+        <v>0.5309054851531982</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>14.07162059211731</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>0.5309054851531982</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>14.07162059211731</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>MHY1771G1026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CMRE</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CMRE</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>COSTAMARE INC.   DL-,0001</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>46052.32911183846</v>
+      </c>
+      <c r="G173" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>1.1937448</v>
+      </c>
+      <c r="J173" t="n">
+        <v>14.20739173062785</v>
+      </c>
+      <c r="K173" t="n">
+        <v>88</v>
+      </c>
+      <c r="L173" t="n">
+        <v>9</v>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>46052.32911183846</v>
+      </c>
+      <c r="N173" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>1.1937448</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>14.20739173062785</v>
+      </c>
+      <c r="R173" t="n">
+        <v>1492.48</v>
+      </c>
+      <c r="S173" t="n">
+        <v>1250.250472295251</v>
+      </c>
+      <c r="T173" t="n">
+        <v>12.78665255756507</v>
+      </c>
+      <c r="U173" t="n">
+        <v>0</v>
+      </c>
+      <c r="V173" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" t="n">
+        <v>9</v>
+      </c>
+      <c r="X173" t="n">
+        <v>-34.36683081738223</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="n">
+        <v>0.5473654866218567</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>14.04996871948242</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>0.5473654866218567</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>14.04996871948242</v>
       </c>
     </row>
   </sheetData>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD173"/>
+  <dimension ref="A1:AD175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17674,7 +17674,7 @@
         <v>9</v>
       </c>
       <c r="M170" s="2" t="n">
-        <v>46052.32911183846</v>
+        <v>46052.32911184028</v>
       </c>
       <c r="N170" t="n">
         <v>19.72</v>
@@ -17780,7 +17780,7 @@
         <v>9</v>
       </c>
       <c r="M171" s="2" t="n">
-        <v>46052.32911183846</v>
+        <v>46052.32911184028</v>
       </c>
       <c r="N171" t="n">
         <v>282.72</v>
@@ -17863,7 +17863,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>46052.32911183846</v>
+        <v>46052.32911184028</v>
       </c>
       <c r="G172" t="n">
         <v>0.595</v>
@@ -17886,7 +17886,7 @@
         <v>10.334</v>
       </c>
       <c r="M172" s="2" t="n">
-        <v>46052.32911183846</v>
+        <v>46052.32911184028</v>
       </c>
       <c r="N172" t="n">
         <v>0.595</v>
@@ -17967,7 +17967,7 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>46052.32911183846</v>
+        <v>46052.32911184028</v>
       </c>
       <c r="G173" t="n">
         <v>16.96</v>
@@ -17990,7 +17990,7 @@
         <v>9</v>
       </c>
       <c r="M173" s="2" t="n">
-        <v>46052.32911183846</v>
+        <v>46052.32911184028</v>
       </c>
       <c r="N173" t="n">
         <v>16.96</v>
@@ -18042,6 +18042,212 @@
       </c>
       <c r="AD173" t="n">
         <v>14.04996871948242</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SE0020050417</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BOL.ST</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BLIDF</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>BOLIDEN AB</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>45972.31283197916</v>
+      </c>
+      <c r="G174" t="n">
+        <v>424.5</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>10.99719</v>
+      </c>
+      <c r="J174" t="n">
+        <v>38.60076983302098</v>
+      </c>
+      <c r="K174" t="n">
+        <v>38</v>
+      </c>
+      <c r="L174" t="n">
+        <v>9</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>46055.33186414053</v>
+      </c>
+      <c r="N174" t="n">
+        <v>626.6</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>10.56894</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>59.28692943663225</v>
+      </c>
+      <c r="R174" t="n">
+        <v>23810.8</v>
+      </c>
+      <c r="S174" t="n">
+        <v>2252.903318592025</v>
+      </c>
+      <c r="T174" t="n">
+        <v>55.71183559424065</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0.4760895170789163</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0.5359001826413139</v>
+      </c>
+      <c r="W174" t="n">
+        <v>7</v>
+      </c>
+      <c r="X174" t="n">
+        <v>-34.36683081738223</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>162.1516854169248</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>0.4372789561748505</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>13.54962468147278</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>0.4164908826351166</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>11.16664576530457</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>NO0010833262</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>KCC.OL</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>KLAVENESS COMB.CARR.  NK1</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>46055.33186414053</v>
+      </c>
+      <c r="G175" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>11.46372</v>
+      </c>
+      <c r="J175" t="n">
+        <v>7.720007118108258</v>
+      </c>
+      <c r="K175" t="n">
+        <v>193</v>
+      </c>
+      <c r="L175" t="n">
+        <v>9</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>46055.33186414053</v>
+      </c>
+      <c r="N175" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>11.46372</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>7.720007118108258</v>
+      </c>
+      <c r="R175" t="n">
+        <v>17080.5</v>
+      </c>
+      <c r="S175" t="n">
+        <v>1489.961373794894</v>
+      </c>
+      <c r="T175" t="n">
+        <v>6.948006406297432</v>
+      </c>
+      <c r="U175" t="n">
+        <v>0</v>
+      </c>
+      <c r="V175" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" t="n">
+        <v>9</v>
+      </c>
+      <c r="X175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="n">
+        <v>0.4645240306854248</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>14.10727548599243</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>0.4645240306854248</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>14.10727548599243</v>
       </c>
     </row>
   </sheetData>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -18094,7 +18094,7 @@
         <v>9</v>
       </c>
       <c r="M174" s="2" t="n">
-        <v>46055.33186414053</v>
+        <v>46055.33186414352</v>
       </c>
       <c r="N174" t="n">
         <v>626.6</v>
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>46055.33186414053</v>
+        <v>46055.33186414352</v>
       </c>
       <c r="G175" t="n">
         <v>88.5</v>
@@ -18196,7 +18196,7 @@
         <v>9</v>
       </c>
       <c r="M175" s="2" t="n">
-        <v>46055.33186414053</v>
+        <v>46055.33186414352</v>
       </c>
       <c r="N175" t="n">
         <v>88.5</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD175"/>
+  <dimension ref="A1:AD177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18250,6 +18250,212 @@
         <v>14.10727548599243</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>BMG3922B1072</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>GENPACT LTD    DL 0,01</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>46051.32973271991</v>
+      </c>
+      <c r="G176" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="J176" t="n">
+        <v>37.39129970086961</v>
+      </c>
+      <c r="K176" t="n">
+        <v>40</v>
+      </c>
+      <c r="L176" t="n">
+        <v>9</v>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>46056.75699037883</v>
+      </c>
+      <c r="N176" t="n">
+        <v>40.02</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>1.1821728</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>33.85291896413113</v>
+      </c>
+      <c r="R176" t="n">
+        <v>1600.8</v>
+      </c>
+      <c r="S176" t="n">
+        <v>1354.116758565245</v>
+      </c>
+      <c r="T176" t="n">
+        <v>33.95946111814177</v>
+      </c>
+      <c r="U176" t="n">
+        <v>-0.1062974542206342</v>
+      </c>
+      <c r="V176" t="n">
+        <v>-0.09463112448739464</v>
+      </c>
+      <c r="W176" t="n">
+        <v>8</v>
+      </c>
+      <c r="X176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>0.5109041333198547</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>14.70826506614685</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>0.5996838212013245</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>14.84443330764771</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>FI4000062195</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>TAALA.HE</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>TAALERI OYJ</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>46056.75699037883</v>
+      </c>
+      <c r="G177" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="K177" t="n">
+        <v>196</v>
+      </c>
+      <c r="L177" t="n">
+        <v>10</v>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>46056.75699037883</v>
+      </c>
+      <c r="N177" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="R177" t="n">
+        <v>1491.56</v>
+      </c>
+      <c r="S177" t="n">
+        <v>1491.56</v>
+      </c>
+      <c r="T177" t="n">
+        <v>6.849</v>
+      </c>
+      <c r="U177" t="n">
+        <v>0</v>
+      </c>
+      <c r="V177" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" t="n">
+        <v>10</v>
+      </c>
+      <c r="X177" t="n">
+        <v>-35.38380736738475</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="n">
+        <v>0.5190487504005432</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>13.95602321624756</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>0.5190487504005432</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>13.95602321624756</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -18300,7 +18300,7 @@
         <v>9</v>
       </c>
       <c r="M176" s="2" t="n">
-        <v>46056.75699037883</v>
+        <v>46056.75699038195</v>
       </c>
       <c r="N176" t="n">
         <v>40.02</v>
@@ -18379,7 +18379,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>46056.75699037883</v>
+        <v>46056.75699038195</v>
       </c>
       <c r="G177" t="n">
         <v>7.61</v>
@@ -18402,7 +18402,7 @@
         <v>10</v>
       </c>
       <c r="M177" s="2" t="n">
-        <v>46056.75699037883</v>
+        <v>46056.75699038195</v>
       </c>
       <c r="N177" t="n">
         <v>7.61</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD177"/>
+  <dimension ref="A1:AD179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18456,6 +18456,216 @@
         <v>13.95602321624756</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>MHY1771G1026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CMRE</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>CMRE</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>COSTAMARE INC.   DL-,0001</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n">
+        <v>46052.32911184028</v>
+      </c>
+      <c r="G178" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>1.1937448</v>
+      </c>
+      <c r="J178" t="n">
+        <v>14.20739173062785</v>
+      </c>
+      <c r="K178" t="n">
+        <v>88</v>
+      </c>
+      <c r="L178" t="n">
+        <v>9</v>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>46058.79753278236</v>
+      </c>
+      <c r="N178" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>1.1799409</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>13.16167614835624</v>
+      </c>
+      <c r="R178" t="n">
+        <v>1366.64</v>
+      </c>
+      <c r="S178" t="n">
+        <v>1158.227501055349</v>
+      </c>
+      <c r="T178" t="n">
+        <v>13.22937567728771</v>
+      </c>
+      <c r="U178" t="n">
+        <v>-0.08431603773584917</v>
+      </c>
+      <c r="V178" t="n">
+        <v>-0.0736036284561149</v>
+      </c>
+      <c r="W178" t="n">
+        <v>9</v>
+      </c>
+      <c r="X178" t="n">
+        <v>-35.38380736738475</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>0.5473654866218567</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>14.04996871948242</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>0.5202584266662598</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>12.69022369384766</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>DK0060696300</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>STG.CO</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>SNDVF</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>SCAND.TOBACCO GROUP DK 1</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>46058.79753278236</v>
+      </c>
+      <c r="G179" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>7.4671</v>
+      </c>
+      <c r="J179" t="n">
+        <v>13.47243240347658</v>
+      </c>
+      <c r="K179" t="n">
+        <v>111</v>
+      </c>
+      <c r="L179" t="n">
+        <v>9</v>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>46058.79753278236</v>
+      </c>
+      <c r="N179" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>7.4671</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>13.47243240347658</v>
+      </c>
+      <c r="R179" t="n">
+        <v>11166.6</v>
+      </c>
+      <c r="S179" t="n">
+        <v>1495.439996785901</v>
+      </c>
+      <c r="T179" t="n">
+        <v>12.12518916312892</v>
+      </c>
+      <c r="U179" t="n">
+        <v>0</v>
+      </c>
+      <c r="V179" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" t="n">
+        <v>9</v>
+      </c>
+      <c r="X179" t="n">
+        <v>-58.38955017736009</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z179" t="inlineStr"/>
+      <c r="AA179" t="n">
+        <v>0.4642572402954102</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>14.33907246589661</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>0.4642572402954102</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>14.33907246589661</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -18506,7 +18506,7 @@
         <v>9</v>
       </c>
       <c r="M178" s="2" t="n">
-        <v>46058.79753278236</v>
+        <v>46058.79753277777</v>
       </c>
       <c r="N178" t="n">
         <v>15.53</v>
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>46058.79753278236</v>
+        <v>46058.79753277777</v>
       </c>
       <c r="G179" t="n">
         <v>100.6</v>
@@ -18612,7 +18612,7 @@
         <v>9</v>
       </c>
       <c r="M179" s="2" t="n">
-        <v>46058.79753278236</v>
+        <v>46058.79753277777</v>
       </c>
       <c r="N179" t="n">
         <v>100.6</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD179"/>
+  <dimension ref="A1:AD185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18666,6 +18666,624 @@
         <v>14.33907246589661</v>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>JE00BLKGSR75</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>IDHC.L</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>IDGXF</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>INTERGRATED DIA.H DL 0,25</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>46052.32911184028</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>1.1937448</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0.498431490549739</v>
+      </c>
+      <c r="K180" t="n">
+        <v>3003</v>
+      </c>
+      <c r="L180" t="n">
+        <v>10.334</v>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>1.1837121</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0.5617920100673128</v>
+      </c>
+      <c r="R180" t="n">
+        <v>1996.995</v>
+      </c>
+      <c r="S180" t="n">
+        <v>1687.061406232141</v>
+      </c>
+      <c r="T180" t="n">
+        <v>0.4951440335905713</v>
+      </c>
+      <c r="U180" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="V180" t="n">
+        <v>0.1271198163015166</v>
+      </c>
+      <c r="W180" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="X180" t="n">
+        <v>-58.38955017736009</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>0.5309054851531982</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>14.07162059211731</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>0.2381956875324249</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>7.013967458724975</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>NO0010833262</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>KCC.OL</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>KLAVENESS COMB.CARR.  NK1</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>46055.33186414352</v>
+      </c>
+      <c r="G181" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>11.46372</v>
+      </c>
+      <c r="J181" t="n">
+        <v>7.720007118108258</v>
+      </c>
+      <c r="K181" t="n">
+        <v>193</v>
+      </c>
+      <c r="L181" t="n">
+        <v>9</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="N181" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>11.2733</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>7.921371736758535</v>
+      </c>
+      <c r="R181" t="n">
+        <v>17234.9</v>
+      </c>
+      <c r="S181" t="n">
+        <v>1528.824745194397</v>
+      </c>
+      <c r="T181" t="n">
+        <v>7.02950764550897</v>
+      </c>
+      <c r="U181" t="n">
+        <v>0.009039548022598876</v>
+      </c>
+      <c r="V181" t="n">
+        <v>0.02608347577529435</v>
+      </c>
+      <c r="W181" t="n">
+        <v>4</v>
+      </c>
+      <c r="X181" t="n">
+        <v>-58.38955017736009</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>0.4645240306854248</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>14.10727548599243</v>
+      </c>
+      <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>FI4000062195</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TAALA.HE</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>TAALERI OYJ</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="n">
+        <v>46056.75699038195</v>
+      </c>
+      <c r="G182" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="K182" t="n">
+        <v>196</v>
+      </c>
+      <c r="L182" t="n">
+        <v>10</v>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="N182" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="R182" t="n">
+        <v>1436.68</v>
+      </c>
+      <c r="S182" t="n">
+        <v>1436.68</v>
+      </c>
+      <c r="T182" t="n">
+        <v>6.984</v>
+      </c>
+      <c r="U182" t="n">
+        <v>-0.03679369250985554</v>
+      </c>
+      <c r="V182" t="n">
+        <v>-0.03679369250985554</v>
+      </c>
+      <c r="W182" t="n">
+        <v>4</v>
+      </c>
+      <c r="X182" t="n">
+        <v>-58.38955017736009</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>0.5190487504005432</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>13.95602321624756</v>
+      </c>
+      <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>US20030N1019</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>COMCAST CORP.   A  DL-,01</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="G183" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>1.1837121</v>
+      </c>
+      <c r="J183" t="n">
+        <v>26.67033647793243</v>
+      </c>
+      <c r="K183" t="n">
+        <v>56</v>
+      </c>
+      <c r="L183" t="n">
+        <v>9</v>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="N183" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>1.1837121</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>26.67033647793243</v>
+      </c>
+      <c r="R183" t="n">
+        <v>1767.92</v>
+      </c>
+      <c r="S183" t="n">
+        <v>1493.538842764216</v>
+      </c>
+      <c r="T183" t="n">
+        <v>24.00330283013919</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" t="n">
+        <v>0</v>
+      </c>
+      <c r="W183" t="n">
+        <v>9</v>
+      </c>
+      <c r="X183" t="n">
+        <v>-14.82579729966571</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z183" t="inlineStr"/>
+      <c r="AA183" t="n">
+        <v>0.4518820941448212</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>13.58432388305664</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>0.4518820941448212</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>13.58432388305664</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>US12653C1080</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CNX</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>CNX</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>CNX RES CORP.      DL-,01</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="G184" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>1.1837121</v>
+      </c>
+      <c r="J184" t="n">
+        <v>34.29888061463594</v>
+      </c>
+      <c r="K184" t="n">
+        <v>43</v>
+      </c>
+      <c r="L184" t="n">
+        <v>10</v>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="N184" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>1.1837121</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>34.29888061463594</v>
+      </c>
+      <c r="R184" t="n">
+        <v>1745.8</v>
+      </c>
+      <c r="S184" t="n">
+        <v>1474.851866429345</v>
+      </c>
+      <c r="T184" t="n">
+        <v>30.86899255317235</v>
+      </c>
+      <c r="U184" t="n">
+        <v>0</v>
+      </c>
+      <c r="V184" t="n">
+        <v>0</v>
+      </c>
+      <c r="W184" t="n">
+        <v>10</v>
+      </c>
+      <c r="X184" t="n">
+        <v>-14.82579729966571</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="n">
+        <v>0.3575266897678375</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>13.30912899971008</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>0.3575266897678375</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>13.30912899971008</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PLKGHM000017</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>KGH.WA</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>KGHPF</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>KGHM POLSKA MIEDZ   ZY 10</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="G185" t="n">
+        <v>305</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>4.21646</v>
+      </c>
+      <c r="J185" t="n">
+        <v>72.33556111050503</v>
+      </c>
+      <c r="K185" t="n">
+        <v>20</v>
+      </c>
+      <c r="L185" t="n">
+        <v>9</v>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>46070.3331393085</v>
+      </c>
+      <c r="N185" t="n">
+        <v>305</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>4.21646</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>72.33556111050503</v>
+      </c>
+      <c r="R185" t="n">
+        <v>6100</v>
+      </c>
+      <c r="S185" t="n">
+        <v>1446.7112222101</v>
+      </c>
+      <c r="T185" t="n">
+        <v>65.10200499945452</v>
+      </c>
+      <c r="U185" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" t="n">
+        <v>0</v>
+      </c>
+      <c r="W185" t="n">
+        <v>9</v>
+      </c>
+      <c r="X185" t="n">
+        <v>-14.82579729966571</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="n">
+        <v>0.4241681098937988</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>13.14046692848206</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>0.4241681098937988</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>13.14046692848206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -18716,7 +18716,7 @@
         <v>10.334</v>
       </c>
       <c r="M180" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="N180" t="n">
         <v>0.665</v>
@@ -18818,7 +18818,7 @@
         <v>9</v>
       </c>
       <c r="M181" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="N181" t="n">
         <v>89.3</v>
@@ -18918,7 +18918,7 @@
         <v>10</v>
       </c>
       <c r="M182" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="N182" t="n">
         <v>7.33</v>
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="G183" t="n">
         <v>31.57</v>
@@ -19022,7 +19022,7 @@
         <v>9</v>
       </c>
       <c r="M183" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="N183" t="n">
         <v>31.57</v>
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="G184" t="n">
         <v>40.6</v>
@@ -19126,7 +19126,7 @@
         <v>10</v>
       </c>
       <c r="M184" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="N184" t="n">
         <v>40.6</v>
@@ -19207,7 +19207,7 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="G185" t="n">
         <v>305</v>
@@ -19230,7 +19230,7 @@
         <v>9</v>
       </c>
       <c r="M185" s="2" t="n">
-        <v>46070.3331393085</v>
+        <v>46070.33313930556</v>
       </c>
       <c r="N185" t="n">
         <v>305</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD185"/>
+  <dimension ref="A1:AD187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19284,6 +19284,216 @@
         <v>13.14046692848206</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>US12653C1080</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CNX</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CNX</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>CNX RES CORP.      DL-,01</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="n">
+        <v>46070.33313930556</v>
+      </c>
+      <c r="G186" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>1.1837121</v>
+      </c>
+      <c r="J186" t="n">
+        <v>34.29888061463594</v>
+      </c>
+      <c r="K186" t="n">
+        <v>43</v>
+      </c>
+      <c r="L186" t="n">
+        <v>10</v>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>46077.33367164168</v>
+      </c>
+      <c r="N186" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>1.1782727</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>32.43731268661321</v>
+      </c>
+      <c r="R186" t="n">
+        <v>1643.46</v>
+      </c>
+      <c r="S186" t="n">
+        <v>1394.804445524368</v>
+      </c>
+      <c r="T186" t="n">
+        <v>31.26641465534405</v>
+      </c>
+      <c r="U186" t="n">
+        <v>-0.05862068965517242</v>
+      </c>
+      <c r="V186" t="n">
+        <v>-0.05427488870375452</v>
+      </c>
+      <c r="W186" t="n">
+        <v>8</v>
+      </c>
+      <c r="X186" t="n">
+        <v>-14.82579729966571</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>0.3575266897678375</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>13.30912899971008</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>0.3147827386856079</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>10.73680192232132</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>US58844R1086</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>MBIN</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>MBIN</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>MERCHANTS BANCORP INC.</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>46077.33367164168</v>
+      </c>
+      <c r="G187" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1.1782727</v>
+      </c>
+      <c r="J187" t="n">
+        <v>36.68929951445026</v>
+      </c>
+      <c r="K187" t="n">
+        <v>40</v>
+      </c>
+      <c r="L187" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>46077.33367164168</v>
+      </c>
+      <c r="N187" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>1.1782727</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>36.68929951445026</v>
+      </c>
+      <c r="R187" t="n">
+        <v>1729.2</v>
+      </c>
+      <c r="S187" t="n">
+        <v>1467.57198057801</v>
+      </c>
+      <c r="T187" t="n">
+        <v>33.02036956300524</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0</v>
+      </c>
+      <c r="V187" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="X187" t="n">
+        <v>-34.83765252591005</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="n">
+        <v>0.441804051399231</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>12.99973482322693</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>0.441804051399231</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>12.99973482322693</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -19334,7 +19334,7 @@
         <v>10</v>
       </c>
       <c r="M186" s="2" t="n">
-        <v>46077.33367164168</v>
+        <v>46077.33367164352</v>
       </c>
       <c r="N186" t="n">
         <v>38.22</v>
@@ -19417,7 +19417,7 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>46077.33367164168</v>
+        <v>46077.33367164352</v>
       </c>
       <c r="G187" t="n">
         <v>43.23</v>
@@ -19440,7 +19440,7 @@
         <v>10.667</v>
       </c>
       <c r="M187" s="2" t="n">
-        <v>46077.33367164168</v>
+        <v>46077.33367164352</v>
       </c>
       <c r="N187" t="n">
         <v>43.23</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD187"/>
+  <dimension ref="A1:AD189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19494,6 +19494,216 @@
         <v>12.99973482322693</v>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>DK0060696300</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>STG.CO</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>SNDVF</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>SCAND.TOBACCO GROUP DK 1</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>46058.79753277777</v>
+      </c>
+      <c r="G188" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>7.4671</v>
+      </c>
+      <c r="J188" t="n">
+        <v>13.47243240347658</v>
+      </c>
+      <c r="K188" t="n">
+        <v>111</v>
+      </c>
+      <c r="L188" t="n">
+        <v>9</v>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>46078.33456228438</v>
+      </c>
+      <c r="N188" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>7.4713</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>13.6254734785111</v>
+      </c>
+      <c r="R188" t="n">
+        <v>11299.8</v>
+      </c>
+      <c r="S188" t="n">
+        <v>1512.427556114732</v>
+      </c>
+      <c r="T188" t="n">
+        <v>12.38454742590956</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0.01192842942345917</v>
+      </c>
+      <c r="V188" t="n">
+        <v>0.01135957267783549</v>
+      </c>
+      <c r="W188" t="n">
+        <v>8</v>
+      </c>
+      <c r="X188" t="n">
+        <v>-34.83765252591005</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>0.4642572402954102</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>14.33907246589661</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>0.1659499853849411</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>8.554148197174072</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>MXP001161019</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ARA.MX</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CNRFF</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>CONSORCIO ARA SAB DE CV</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>46078.33456228438</v>
+      </c>
+      <c r="G189" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>20.24964</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0.2172878135117464</v>
+      </c>
+      <c r="K189" t="n">
+        <v>6889</v>
+      </c>
+      <c r="L189" t="n">
+        <v>9</v>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>46078.33456228438</v>
+      </c>
+      <c r="N189" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>20.24964</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0.2172878135117464</v>
+      </c>
+      <c r="R189" t="n">
+        <v>30311.6</v>
+      </c>
+      <c r="S189" t="n">
+        <v>1496.895747282421</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0.1955590321605717</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" t="n">
+        <v>0</v>
+      </c>
+      <c r="W189" t="n">
+        <v>9</v>
+      </c>
+      <c r="X189" t="n">
+        <v>-30.59076269370205</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="n">
+        <v>0.2926181554794312</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>11.28957903385162</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>0.2926181554794312</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>11.28957903385162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -19544,7 +19544,7 @@
         <v>9</v>
       </c>
       <c r="M188" s="2" t="n">
-        <v>46078.33456228438</v>
+        <v>46078.33456228009</v>
       </c>
       <c r="N188" t="n">
         <v>101.8</v>
@@ -19627,7 +19627,7 @@
         </is>
       </c>
       <c r="F189" s="2" t="n">
-        <v>46078.33456228438</v>
+        <v>46078.33456228009</v>
       </c>
       <c r="G189" t="n">
         <v>4.4</v>
@@ -19650,7 +19650,7 @@
         <v>9</v>
       </c>
       <c r="M189" s="2" t="n">
-        <v>46078.33456228438</v>
+        <v>46078.33456228009</v>
       </c>
       <c r="N189" t="n">
         <v>4.4</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD189"/>
+  <dimension ref="A1:AD192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19704,6 +19704,324 @@
         <v>11.28957903385162</v>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>FR0000051070</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>MAU.PA</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>MRELF</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>MAUREL ET PROM INH.EO-,77</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>46048.31877523148</v>
+      </c>
+      <c r="G190" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="K190" t="n">
+        <v>236</v>
+      </c>
+      <c r="L190" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>46083.33158142614</v>
+      </c>
+      <c r="N190" t="n">
+        <v>8.925000000000001</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>8.925000000000001</v>
+      </c>
+      <c r="R190" t="n">
+        <v>2106.3</v>
+      </c>
+      <c r="S190" t="n">
+        <v>2106.3</v>
+      </c>
+      <c r="T190" t="n">
+        <v>8.289000000000001</v>
+      </c>
+      <c r="U190" t="n">
+        <v>0.4077287066246058</v>
+      </c>
+      <c r="V190" t="n">
+        <v>0.4077287066246058</v>
+      </c>
+      <c r="W190" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="X190" t="n">
+        <v>-30.59076269370205</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>121.924237306298</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>0.4323444068431854</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>11.98598069381714</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>0.2357313185930252</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>8.931247417449951</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>US80007P8692</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>SANDRIDGE ENERGY  DL-,001</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>46051.32973271991</v>
+      </c>
+      <c r="G191" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>1.1976048</v>
+      </c>
+      <c r="J191" t="n">
+        <v>12.94249989646</v>
+      </c>
+      <c r="K191" t="n">
+        <v>115</v>
+      </c>
+      <c r="L191" t="n">
+        <v>12</v>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>46083.33158142614</v>
+      </c>
+      <c r="N191" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>1.1716461</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>14.96185580270356</v>
+      </c>
+      <c r="R191" t="n">
+        <v>2015.95</v>
+      </c>
+      <c r="S191" t="n">
+        <v>1720.61341731091</v>
+      </c>
+      <c r="T191" t="n">
+        <v>13.47612920156017</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0.130967741935484</v>
+      </c>
+      <c r="V191" t="n">
+        <v>0.1560251823371381</v>
+      </c>
+      <c r="W191" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="X191" t="n">
+        <v>-30.59076269370205</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>58.05648230450248</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>0.4404408931732178</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>14.46690368652344</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>0.2406706213951111</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>8.153540555953979</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PLKGHM000017</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>KGH.WA</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>KGHPF</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>KGHM POLSKA MIEDZ   ZY 10</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>46070.33313930556</v>
+      </c>
+      <c r="G192" t="n">
+        <v>305</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>4.21646</v>
+      </c>
+      <c r="J192" t="n">
+        <v>72.33556111050503</v>
+      </c>
+      <c r="K192" t="n">
+        <v>20</v>
+      </c>
+      <c r="L192" t="n">
+        <v>9</v>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>46083.33158142614</v>
+      </c>
+      <c r="N192" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>4.23234</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>79.27056899965504</v>
+      </c>
+      <c r="R192" t="n">
+        <v>6710</v>
+      </c>
+      <c r="S192" t="n">
+        <v>1585.411379993101</v>
+      </c>
+      <c r="T192" t="n">
+        <v>73.04397351622013</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="V192" t="n">
+        <v>0.09587273234191951</v>
+      </c>
+      <c r="W192" t="n">
+        <v>8</v>
+      </c>
+      <c r="X192" t="n">
+        <v>-30.59076269370205</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>34.67503944575007</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>0.4241681098937988</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>13.14046692848206</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>0.2189548164606094</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>8.861581921577454</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -19754,7 +19754,7 @@
         <v>9.667</v>
       </c>
       <c r="M190" s="2" t="n">
-        <v>46083.33158142614</v>
+        <v>46083.33158142361</v>
       </c>
       <c r="N190" t="n">
         <v>8.925000000000001</v>
@@ -19860,7 +19860,7 @@
         <v>12</v>
       </c>
       <c r="M191" s="2" t="n">
-        <v>46083.33158142614</v>
+        <v>46083.33158142361</v>
       </c>
       <c r="N191" t="n">
         <v>17.53</v>
@@ -19966,7 +19966,7 @@
         <v>9</v>
       </c>
       <c r="M192" s="2" t="n">
-        <v>46083.33158142614</v>
+        <v>46083.33158142361</v>
       </c>
       <c r="N192" t="n">
         <v>335.5</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD192"/>
+  <dimension ref="A1:AD196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20022,6 +20022,424 @@
         <v>8.861581921577454</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>MXP001161019</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ARA.MX</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>CNRFF</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>CONSORCIO ARA SAB DE CV</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>46078.33456228009</v>
+      </c>
+      <c r="G193" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>20.24964</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0.2172878135117464</v>
+      </c>
+      <c r="K193" t="n">
+        <v>6889</v>
+      </c>
+      <c r="L193" t="n">
+        <v>9</v>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>46087.32869898473</v>
+      </c>
+      <c r="N193" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>20.48808</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0.2123185774362458</v>
+      </c>
+      <c r="R193" t="n">
+        <v>29967.15</v>
+      </c>
+      <c r="S193" t="n">
+        <v>1462.662679958298</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0.2145110534629447</v>
+      </c>
+      <c r="U193" t="n">
+        <v>-0.01136363636363658</v>
+      </c>
+      <c r="V193" t="n">
+        <v>-0.02286937309179526</v>
+      </c>
+      <c r="W193" t="n">
+        <v>9</v>
+      </c>
+      <c r="X193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>0.2926181554794312</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>11.28957903385162</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>0.2615714073181152</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>10.67705935239792</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>US57686G1058</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>MATX</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>MATX</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>MATSON INC.</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>46087.32869898473</v>
+      </c>
+      <c r="G194" t="n">
+        <v>158.75</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>1.1615751</v>
+      </c>
+      <c r="J194" t="n">
+        <v>136.6678745093623</v>
+      </c>
+      <c r="K194" t="n">
+        <v>10</v>
+      </c>
+      <c r="L194" t="n">
+        <v>10</v>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>46087.32869898473</v>
+      </c>
+      <c r="N194" t="n">
+        <v>158.75</v>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>1.1615751</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>136.6678745093623</v>
+      </c>
+      <c r="R194" t="n">
+        <v>1587.5</v>
+      </c>
+      <c r="S194" t="n">
+        <v>1366.678745093623</v>
+      </c>
+      <c r="T194" t="n">
+        <v>123.0010870584261</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" t="n">
+        <v>10</v>
+      </c>
+      <c r="X194" t="n">
+        <v>-8.558266831030849</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="n">
+        <v>0.2826876938343048</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>12.10070085525513</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>0.2826876938343048</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>12.10070085525513</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>NO0011082075</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>HAUTO.OL</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>HOEGF</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>HOEGH AUTOLINERS     NK 1</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="n">
+        <v>46087.32869898473</v>
+      </c>
+      <c r="G195" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>11.19962</v>
+      </c>
+      <c r="J195" t="n">
+        <v>11.89326066420111</v>
+      </c>
+      <c r="K195" t="n">
+        <v>125</v>
+      </c>
+      <c r="L195" t="n">
+        <v>9</v>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>46087.32869898473</v>
+      </c>
+      <c r="N195" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>11.19962</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>11.89326066420111</v>
+      </c>
+      <c r="R195" t="n">
+        <v>16650</v>
+      </c>
+      <c r="S195" t="n">
+        <v>1486.657583025138</v>
+      </c>
+      <c r="T195" t="n">
+        <v>10.703934597781</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
+      <c r="V195" t="n">
+        <v>0</v>
+      </c>
+      <c r="W195" t="n">
+        <v>9</v>
+      </c>
+      <c r="X195" t="n">
+        <v>-8.558266831030849</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="n">
+        <v>0.2970967888832092</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>11.23735225200653</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>0.2970967888832092</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>11.23735225200653</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>JP3362700001</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>9104.T</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>MSLOF</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>MITSUI OSK LINES</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>46087.32869898473</v>
+      </c>
+      <c r="G196" t="n">
+        <v>5958</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>183</v>
+      </c>
+      <c r="J196" t="n">
+        <v>32.55737704918032</v>
+      </c>
+      <c r="K196" t="n">
+        <v>45</v>
+      </c>
+      <c r="L196" t="n">
+        <v>9</v>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>46087.32869898473</v>
+      </c>
+      <c r="N196" t="n">
+        <v>5958</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>32.55737704918032</v>
+      </c>
+      <c r="R196" t="n">
+        <v>268110</v>
+      </c>
+      <c r="S196" t="n">
+        <v>1465.081967213115</v>
+      </c>
+      <c r="T196" t="n">
+        <v>29.30163934426229</v>
+      </c>
+      <c r="U196" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" t="n">
+        <v>0</v>
+      </c>
+      <c r="W196" t="n">
+        <v>9</v>
+      </c>
+      <c r="X196" t="n">
+        <v>-8.558266831030849</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="n">
+        <v>0.2755848467350006</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>11.05543410778046</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>0.2755848467350006</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>11.05543410778046</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -20072,7 +20072,7 @@
         <v>9</v>
       </c>
       <c r="M193" s="2" t="n">
-        <v>46087.32869898473</v>
+        <v>46087.32869898148</v>
       </c>
       <c r="N193" t="n">
         <v>4.35</v>
@@ -20155,7 +20155,7 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>46087.32869898473</v>
+        <v>46087.32869898148</v>
       </c>
       <c r="G194" t="n">
         <v>158.75</v>
@@ -20178,7 +20178,7 @@
         <v>10</v>
       </c>
       <c r="M194" s="2" t="n">
-        <v>46087.32869898473</v>
+        <v>46087.32869898148</v>
       </c>
       <c r="N194" t="n">
         <v>158.75</v>
@@ -20259,7 +20259,7 @@
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>46087.32869898473</v>
+        <v>46087.32869898148</v>
       </c>
       <c r="G195" t="n">
         <v>133.2</v>
@@ -20282,7 +20282,7 @@
         <v>9</v>
       </c>
       <c r="M195" s="2" t="n">
-        <v>46087.32869898473</v>
+        <v>46087.32869898148</v>
       </c>
       <c r="N195" t="n">
         <v>133.2</v>
@@ -20363,7 +20363,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>46087.32869898473</v>
+        <v>46087.32869898148</v>
       </c>
       <c r="G196" t="n">
         <v>5958</v>
@@ -20386,7 +20386,7 @@
         <v>9</v>
       </c>
       <c r="M196" s="2" t="n">
-        <v>46087.32869898473</v>
+        <v>46087.32869898148</v>
       </c>
       <c r="N196" t="n">
         <v>5958</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD196"/>
+  <dimension ref="A1:AD198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20440,6 +20440,214 @@
         <v>11.05543410778046</v>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>US92343V1044</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>VERIZON COMM. INC. DL-,10</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="n">
+        <v>46090.33189306255</v>
+      </c>
+      <c r="G197" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>1.156738</v>
+      </c>
+      <c r="J197" t="n">
+        <v>44.19323995580675</v>
+      </c>
+      <c r="K197" t="n">
+        <v>33</v>
+      </c>
+      <c r="L197" t="n">
+        <v>10</v>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>46090.33189306255</v>
+      </c>
+      <c r="N197" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>1.156738</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>44.19323995580675</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1686.96</v>
+      </c>
+      <c r="S197" t="n">
+        <v>1458.376918541623</v>
+      </c>
+      <c r="T197" t="n">
+        <v>39.77391596022608</v>
+      </c>
+      <c r="U197" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" t="n">
+        <v>10</v>
+      </c>
+      <c r="X197" t="n">
+        <v>-8.558266831030849</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="n">
+        <v>0.2994548678398132</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>12.33165961503983</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>0.2994548678398132</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>12.33165961503983</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>US2925541029</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ECPG</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ECPG</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ENCORE CAP.        DL-,01</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="n">
+        <v>46090.33189306255</v>
+      </c>
+      <c r="G198" t="n">
+        <v>70.68000000000001</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1.156738</v>
+      </c>
+      <c r="J198" t="n">
+        <v>61.10285993889715</v>
+      </c>
+      <c r="K198" t="n">
+        <v>18</v>
+      </c>
+      <c r="L198" t="n">
+        <v>11</v>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>46090.33189306255</v>
+      </c>
+      <c r="N198" t="n">
+        <v>70.68000000000001</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>1.156738</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>61.10285993889715</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1272.24</v>
+      </c>
+      <c r="S198" t="n">
+        <v>1099.851478900149</v>
+      </c>
+      <c r="T198" t="n">
+        <v>54.99257394500744</v>
+      </c>
+      <c r="U198" t="n">
+        <v>0</v>
+      </c>
+      <c r="V198" t="n">
+        <v>0</v>
+      </c>
+      <c r="W198" t="n">
+        <v>11</v>
+      </c>
+      <c r="X198" t="n">
+        <v>-8.558266831030849</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="n">
+        <v>0.3177817463874817</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>11.62710583209991</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>0.3177817463874817</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>11.62710583209991</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -20467,7 +20467,7 @@
         </is>
       </c>
       <c r="F197" s="2" t="n">
-        <v>46090.33189306255</v>
+        <v>46090.33189306713</v>
       </c>
       <c r="G197" t="n">
         <v>51.12</v>
@@ -20490,7 +20490,7 @@
         <v>10</v>
       </c>
       <c r="M197" s="2" t="n">
-        <v>46090.33189306255</v>
+        <v>46090.33189306713</v>
       </c>
       <c r="N197" t="n">
         <v>51.12</v>
@@ -20571,7 +20571,7 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>46090.33189306255</v>
+        <v>46090.33189306713</v>
       </c>
       <c r="G198" t="n">
         <v>70.68000000000001</v>
@@ -20594,7 +20594,7 @@
         <v>11</v>
       </c>
       <c r="M198" s="2" t="n">
-        <v>46090.33189306255</v>
+        <v>46090.33189306713</v>
       </c>
       <c r="N198" t="n">
         <v>70.68000000000001</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD198"/>
+  <dimension ref="A1:AD200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20648,6 +20648,216 @@
         <v>11.62710583209991</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>US58844R1086</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>MBIN</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>MBIN</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>MERCHANTS BANCORP INC.</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="n">
+        <v>46077.33367164352</v>
+      </c>
+      <c r="G199" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>1.1782727</v>
+      </c>
+      <c r="J199" t="n">
+        <v>36.68929951445026</v>
+      </c>
+      <c r="K199" t="n">
+        <v>40</v>
+      </c>
+      <c r="L199" t="n">
+        <v>10.667</v>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>46092.33080178414</v>
+      </c>
+      <c r="N199" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>1.16198</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>36.05053443260641</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1675.6</v>
+      </c>
+      <c r="S199" t="n">
+        <v>1442.021377304256</v>
+      </c>
+      <c r="T199" t="n">
+        <v>33.65819970549075</v>
+      </c>
+      <c r="U199" t="n">
+        <v>-0.03099699282905377</v>
+      </c>
+      <c r="V199" t="n">
+        <v>-0.01741011930719116</v>
+      </c>
+      <c r="W199" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="X199" t="n">
+        <v>-8.558266831030849</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>0.441804051399231</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>12.99973482322693</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>0.3033895194530487</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>9.028658036708832</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>NO0010096985</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>EQNR.OL</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>STOHF</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>EQUINOR ASA       NK 2,50</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>46092.33080178414</v>
+      </c>
+      <c r="G200" t="n">
+        <v>313.1</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>11.1594</v>
+      </c>
+      <c r="J200" t="n">
+        <v>28.05706399985663</v>
+      </c>
+      <c r="K200" t="n">
+        <v>52</v>
+      </c>
+      <c r="L200" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>46092.33080178414</v>
+      </c>
+      <c r="N200" t="n">
+        <v>313.1</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>11.1594</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>28.05706399985663</v>
+      </c>
+      <c r="R200" t="n">
+        <v>16281.2</v>
+      </c>
+      <c r="S200" t="n">
+        <v>1458.967327992545</v>
+      </c>
+      <c r="T200" t="n">
+        <v>25.25135759987096</v>
+      </c>
+      <c r="U200" t="n">
+        <v>0</v>
+      </c>
+      <c r="V200" t="n">
+        <v>0</v>
+      </c>
+      <c r="W200" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="X200" t="n">
+        <v>-14.94591764946935</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="n">
+        <v>0.3370742499828339</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>12.57034326028824</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>0.3370742499828339</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>12.57034326028824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -20698,7 +20698,7 @@
         <v>10.667</v>
       </c>
       <c r="M199" s="2" t="n">
-        <v>46092.33080178414</v>
+        <v>46092.33080178241</v>
       </c>
       <c r="N199" t="n">
         <v>41.89</v>
@@ -20781,7 +20781,7 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>46092.33080178414</v>
+        <v>46092.33080178241</v>
       </c>
       <c r="G200" t="n">
         <v>313.1</v>
@@ -20804,7 +20804,7 @@
         <v>9.667</v>
       </c>
       <c r="M200" s="2" t="n">
-        <v>46092.33080178414</v>
+        <v>46092.33080178241</v>
       </c>
       <c r="N200" t="n">
         <v>313.1</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD200"/>
+  <dimension ref="A1:AD202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20858,6 +20858,216 @@
         <v>12.57034326028824</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>US92343V1044</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>VZ</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>VERIZON COMM. INC. DL-,10</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="n">
+        <v>46090.33189306713</v>
+      </c>
+      <c r="G201" t="n">
+        <v>51.12</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>1.156738</v>
+      </c>
+      <c r="J201" t="n">
+        <v>44.19323995580675</v>
+      </c>
+      <c r="K201" t="n">
+        <v>33</v>
+      </c>
+      <c r="L201" t="n">
+        <v>10</v>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>46093.33119489161</v>
+      </c>
+      <c r="N201" t="n">
+        <v>50.68</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>1.1551346</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>43.87367498125327</v>
+      </c>
+      <c r="R201" t="n">
+        <v>1672.44</v>
+      </c>
+      <c r="S201" t="n">
+        <v>1447.831274381358</v>
+      </c>
+      <c r="T201" t="n">
+        <v>39.87973669388245</v>
+      </c>
+      <c r="U201" t="n">
+        <v>-0.008607198748043721</v>
+      </c>
+      <c r="V201" t="n">
+        <v>-0.007231082737383598</v>
+      </c>
+      <c r="W201" t="n">
+        <v>8</v>
+      </c>
+      <c r="X201" t="n">
+        <v>-14.94591764946935</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>0.2994548678398132</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>12.33165961503983</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>0.3621533811092377</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>11.45912432670593</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>LU2598331598</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>TEN.MI</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>TNRSF</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>TENARIS S.A. DL 1</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="n">
+        <v>46093.33119489161</v>
+      </c>
+      <c r="G202" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J202" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="K202" t="n">
+        <v>62</v>
+      </c>
+      <c r="L202" t="n">
+        <v>9</v>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>46093.33119489161</v>
+      </c>
+      <c r="N202" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="R202" t="n">
+        <v>1445.84</v>
+      </c>
+      <c r="S202" t="n">
+        <v>1445.84</v>
+      </c>
+      <c r="T202" t="n">
+        <v>20.988</v>
+      </c>
+      <c r="U202" t="n">
+        <v>0</v>
+      </c>
+      <c r="V202" t="n">
+        <v>0</v>
+      </c>
+      <c r="W202" t="n">
+        <v>9</v>
+      </c>
+      <c r="X202" t="n">
+        <v>-17.58232868953561</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="n">
+        <v>0.3601253628730774</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>12.53990530967712</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>0.3601253628730774</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>12.53990530967712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -20908,7 +20908,7 @@
         <v>10</v>
       </c>
       <c r="M201" s="2" t="n">
-        <v>46093.33119489161</v>
+        <v>46093.33119489584</v>
       </c>
       <c r="N201" t="n">
         <v>50.68</v>
@@ -20991,7 +20991,7 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>46093.33119489161</v>
+        <v>46093.33119489584</v>
       </c>
       <c r="G202" t="n">
         <v>23.32</v>
@@ -21014,7 +21014,7 @@
         <v>9</v>
       </c>
       <c r="M202" s="2" t="n">
-        <v>46093.33119489161</v>
+        <v>46093.33119489584</v>
       </c>
       <c r="N202" t="n">
         <v>23.32</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD202"/>
+  <dimension ref="A1:AD204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21068,6 +21068,216 @@
         <v>12.53990530967712</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>NO0011082075</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>HAUTO.OL</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>HOEGF</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>HOEGH AUTOLINERS     NK 1</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="n">
+        <v>46087.32869898148</v>
+      </c>
+      <c r="G203" t="n">
+        <v>133.2</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>11.19962</v>
+      </c>
+      <c r="J203" t="n">
+        <v>11.89326066420111</v>
+      </c>
+      <c r="K203" t="n">
+        <v>125</v>
+      </c>
+      <c r="L203" t="n">
+        <v>9</v>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>46094.45721853803</v>
+      </c>
+      <c r="N203" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>11.17993</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>10.83191039657672</v>
+      </c>
+      <c r="R203" t="n">
+        <v>15137.5</v>
+      </c>
+      <c r="S203" t="n">
+        <v>1353.98879957209</v>
+      </c>
+      <c r="T203" t="n">
+        <v>10.86658605401048</v>
+      </c>
+      <c r="U203" t="n">
+        <v>-0.09084084084084076</v>
+      </c>
+      <c r="V203" t="n">
+        <v>-0.08923963726945494</v>
+      </c>
+      <c r="W203" t="n">
+        <v>8</v>
+      </c>
+      <c r="X203" t="n">
+        <v>-17.58232868953561</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>0.2970967888832092</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>11.23735225200653</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>0.5190789699554443</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>13.80146908760071</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>FR0004125920</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AMUN.PA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>AMDUF</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AMUNDI S.A.      EO 2,50</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="n">
+        <v>46094.45721853803</v>
+      </c>
+      <c r="G204" t="n">
+        <v>73</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>73</v>
+      </c>
+      <c r="K204" t="n">
+        <v>18</v>
+      </c>
+      <c r="L204" t="n">
+        <v>9</v>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>46094.45721853803</v>
+      </c>
+      <c r="N204" t="n">
+        <v>73</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>73</v>
+      </c>
+      <c r="R204" t="n">
+        <v>1314</v>
+      </c>
+      <c r="S204" t="n">
+        <v>1314</v>
+      </c>
+      <c r="T204" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="U204" t="n">
+        <v>0</v>
+      </c>
+      <c r="V204" t="n">
+        <v>0</v>
+      </c>
+      <c r="W204" t="n">
+        <v>9</v>
+      </c>
+      <c r="X204" t="n">
+        <v>-50.74952455279772</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="n">
+        <v>0.339430958032608</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>12.6814751625061</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>0.339430958032608</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>12.6814751625061</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -21118,7 +21118,7 @@
         <v>9</v>
       </c>
       <c r="M203" s="2" t="n">
-        <v>46094.45721853803</v>
+        <v>46094.45721854167</v>
       </c>
       <c r="N203" t="n">
         <v>121.1</v>
@@ -21201,7 +21201,7 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>46094.45721853803</v>
+        <v>46094.45721854167</v>
       </c>
       <c r="G204" t="n">
         <v>73</v>
@@ -21224,7 +21224,7 @@
         <v>9</v>
       </c>
       <c r="M204" s="2" t="n">
-        <v>46094.45721853803</v>
+        <v>46094.45721854167</v>
       </c>
       <c r="N204" t="n">
         <v>73</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD204"/>
+  <dimension ref="A1:AD206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21278,6 +21278,216 @@
         <v>12.6814751625061</v>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>NO0010096985</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>EQNR.OL</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>STOHF</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>EQUINOR ASA       NK 2,50</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>46092.33080178241</v>
+      </c>
+      <c r="G205" t="n">
+        <v>313.1</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>11.1594</v>
+      </c>
+      <c r="J205" t="n">
+        <v>28.05706399985663</v>
+      </c>
+      <c r="K205" t="n">
+        <v>52</v>
+      </c>
+      <c r="L205" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>46100.33122857202</v>
+      </c>
+      <c r="N205" t="n">
+        <v>359</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>10.9703</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>32.7247203813934</v>
+      </c>
+      <c r="R205" t="n">
+        <v>18668</v>
+      </c>
+      <c r="S205" t="n">
+        <v>1701.685459832457</v>
+      </c>
+      <c r="T205" t="n">
+        <v>29.364184964374</v>
+      </c>
+      <c r="U205" t="n">
+        <v>0.146598530820824</v>
+      </c>
+      <c r="V205" t="n">
+        <v>0.1663629659026555</v>
+      </c>
+      <c r="W205" t="n">
+        <v>6.001</v>
+      </c>
+      <c r="X205" t="n">
+        <v>-50.74952455279772</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>9.930008407180232</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>0.3370742499828339</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>12.57034326028824</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>0.3920232057571411</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>9.851851178169252</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>US71654V4086</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>PETROLEO BRASILEIRO ADR/2</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>46100.33122857202</v>
+      </c>
+      <c r="G206" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>1.1458691</v>
+      </c>
+      <c r="J206" t="n">
+        <v>17.25327962853698</v>
+      </c>
+      <c r="K206" t="n">
+        <v>86</v>
+      </c>
+      <c r="L206" t="n">
+        <v>11</v>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>46100.33122857202</v>
+      </c>
+      <c r="N206" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>1.1458691</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>17.25327962853698</v>
+      </c>
+      <c r="R206" t="n">
+        <v>1700.22</v>
+      </c>
+      <c r="S206" t="n">
+        <v>1483.78204805418</v>
+      </c>
+      <c r="T206" t="n">
+        <v>15.52795166568328</v>
+      </c>
+      <c r="U206" t="n">
+        <v>0</v>
+      </c>
+      <c r="V206" t="n">
+        <v>0</v>
+      </c>
+      <c r="W206" t="n">
+        <v>11</v>
+      </c>
+      <c r="X206" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="n">
+        <v>0.373985767364502</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>14.50431931018829</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>0.373985767364502</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>14.50431931018829</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -21328,7 +21328,7 @@
         <v>9.667</v>
       </c>
       <c r="M205" s="2" t="n">
-        <v>46100.33122857202</v>
+        <v>46100.33122857639</v>
       </c>
       <c r="N205" t="n">
         <v>359</v>
@@ -21411,7 +21411,7 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>46100.33122857202</v>
+        <v>46100.33122857639</v>
       </c>
       <c r="G206" t="n">
         <v>19.77</v>
@@ -21434,7 +21434,7 @@
         <v>11</v>
       </c>
       <c r="M206" s="2" t="n">
-        <v>46100.33122857202</v>
+        <v>46100.33122857639</v>
       </c>
       <c r="N206" t="n">
         <v>19.77</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD206"/>
+  <dimension ref="A1:AD209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21488,6 +21488,316 @@
         <v>14.50431931018829</v>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>US20030N1019</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>COMCAST CORP.   A  DL-,01</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>46070.33313930556</v>
+      </c>
+      <c r="G207" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>1.1837121</v>
+      </c>
+      <c r="J207" t="n">
+        <v>26.67033647793243</v>
+      </c>
+      <c r="K207" t="n">
+        <v>56</v>
+      </c>
+      <c r="L207" t="n">
+        <v>9</v>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>46100.41828139728</v>
+      </c>
+      <c r="N207" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>1.1481056</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>24.88447055741214</v>
+      </c>
+      <c r="R207" t="n">
+        <v>1599.92</v>
+      </c>
+      <c r="S207" t="n">
+        <v>1393.53035121508</v>
+      </c>
+      <c r="T207" t="n">
+        <v>24.89363063188163</v>
+      </c>
+      <c r="U207" t="n">
+        <v>-0.09502692429521697</v>
+      </c>
+      <c r="V207" t="n">
+        <v>-0.0669607570192432</v>
+      </c>
+      <c r="W207" t="n">
+        <v>8</v>
+      </c>
+      <c r="X207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>0.4518820941448212</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>13.58432388305664</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>0.381274402141571</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>12.17031121253967</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>GB00BN7SWP63</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>GSK.L</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>GLAXF</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>GSK PLC  LS-,3125</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>46100.41828139728</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1953</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>0.86403</v>
+      </c>
+      <c r="J208" t="n">
+        <v>2260.33818270199</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>10</v>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>46100.41828139728</v>
+      </c>
+      <c r="N208" t="n">
+        <v>1953</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>0.86403</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>2260.33818270199</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>2034.304364431791</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" t="n">
+        <v>0</v>
+      </c>
+      <c r="W208" t="n">
+        <v>10</v>
+      </c>
+      <c r="X208" t="n">
+        <v>-25.00212288728407</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="n">
+        <v>0.4093043804168701</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>14.37390947341919</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>0.4093043804168701</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>14.37390947341919</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>BRPETRACNPR6</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PETR4.SA</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>PETROLEO BRAS.SA PET.PFD</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>46100.41828139728</v>
+      </c>
+      <c r="G209" t="n">
+        <v>47</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>5.996</v>
+      </c>
+      <c r="J209" t="n">
+        <v>7.838559039359573</v>
+      </c>
+      <c r="K209" t="n">
+        <v>190</v>
+      </c>
+      <c r="L209" t="n">
+        <v>10</v>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>46100.41828139728</v>
+      </c>
+      <c r="N209" t="n">
+        <v>47</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>5.996</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>7.838559039359573</v>
+      </c>
+      <c r="R209" t="n">
+        <v>8930</v>
+      </c>
+      <c r="S209" t="n">
+        <v>1489.326217478319</v>
+      </c>
+      <c r="T209" t="n">
+        <v>7.054703135423615</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>0</v>
+      </c>
+      <c r="W209" t="n">
+        <v>10</v>
+      </c>
+      <c r="X209" t="n">
+        <v>-25.00212288728407</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="n">
+        <v>0.3743711411952972</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>13.56762742996216</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>0.3743711411952972</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>13.56762742996216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -21538,7 +21538,7 @@
         <v>9</v>
       </c>
       <c r="M207" s="2" t="n">
-        <v>46100.41828139728</v>
+        <v>46100.41828140046</v>
       </c>
       <c r="N207" t="n">
         <v>28.57</v>
@@ -21621,7 +21621,7 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>46100.41828139728</v>
+        <v>46100.41828140046</v>
       </c>
       <c r="G208" t="n">
         <v>1953</v>
@@ -21644,7 +21644,7 @@
         <v>10</v>
       </c>
       <c r="M208" s="2" t="n">
-        <v>46100.41828139728</v>
+        <v>46100.41828140046</v>
       </c>
       <c r="N208" t="n">
         <v>1953</v>
@@ -21721,7 +21721,7 @@
         </is>
       </c>
       <c r="F209" s="2" t="n">
-        <v>46100.41828139728</v>
+        <v>46100.41828140046</v>
       </c>
       <c r="G209" t="n">
         <v>47</v>
@@ -21744,7 +21744,7 @@
         <v>10</v>
       </c>
       <c r="M209" s="2" t="n">
-        <v>46100.41828139728</v>
+        <v>46100.41828140046</v>
       </c>
       <c r="N209" t="n">
         <v>47</v>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD209"/>
+  <dimension ref="A1:AD211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21798,6 +21798,212 @@
         <v>13.56762742996216</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>sell</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>BRPETRACNPR6</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>PETR4.SA</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>PETROLEO BRAS.SA PET.PFD</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>46100.41828140046</v>
+      </c>
+      <c r="G210" t="n">
+        <v>47</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>5.996</v>
+      </c>
+      <c r="J210" t="n">
+        <v>7.838559039359573</v>
+      </c>
+      <c r="K210" t="n">
+        <v>190</v>
+      </c>
+      <c r="L210" t="n">
+        <v>10</v>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>46104.34027044588</v>
+      </c>
+      <c r="N210" t="n">
+        <v>45.67</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>6.1149</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>7.468642169127869</v>
+      </c>
+      <c r="R210" t="n">
+        <v>8677.300000000001</v>
+      </c>
+      <c r="S210" t="n">
+        <v>1419.042012134295</v>
+      </c>
+      <c r="T210" t="n">
+        <v>7.154400198691944</v>
+      </c>
+      <c r="U210" t="n">
+        <v>-0.02829787234042547</v>
+      </c>
+      <c r="V210" t="n">
+        <v>-0.04719194795551696</v>
+      </c>
+      <c r="W210" t="n">
+        <v>8</v>
+      </c>
+      <c r="X210" t="n">
+        <v>-25.00212288728407</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>0.3743711411952972</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>13.56762742996216</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>0.3686025738716125</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>11.49500751495361</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>buy</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>US2810201077</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>EIX</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>EDISON INTL</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>46104.34027044588</v>
+      </c>
+      <c r="G211" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>1.1536686</v>
+      </c>
+      <c r="J211" t="n">
+        <v>60.45930347761913</v>
+      </c>
+      <c r="K211" t="n">
+        <v>24</v>
+      </c>
+      <c r="L211" t="n">
+        <v>9</v>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>46104.34027044588</v>
+      </c>
+      <c r="N211" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>1.1536686</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>60.45930347761913</v>
+      </c>
+      <c r="R211" t="n">
+        <v>1674</v>
+      </c>
+      <c r="S211" t="n">
+        <v>1451.023283462859</v>
+      </c>
+      <c r="T211" t="n">
+        <v>54.41337312985722</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" t="n">
+        <v>9</v>
+      </c>
+      <c r="X211" t="n">
+        <v>-42.57317422329002</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="n">
+        <v>0.4689008295536041</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>14.22513294219971</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>0.4689008295536041</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>14.22513294219971</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -21844,7 +21844,7 @@
         <v>10</v>
       </c>
       <c r="M210" s="2" t="n">
-        <v>46104.34027044588</v>
+        <v>46104.34027045139</v>
       </c>
       <c r="N210" t="n">
         <v>45.67</v>
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="F211" s="2" t="n">
-        <v>46104.34027044588</v>
+        <v>46104.34027045139</v>
       </c>
       <c r="G211" t="n">
         <v>69.75</v>
@@ -21950,7 +21950,7 @@
         <v>9</v>
       </c>
       <c r="M211" s="2" t="n">
-        <v>46104.34027044588</v>
+        <v>46104.34027045139</v>
       </c>
       <c r="N211" t="n">
         <v>69.75</v>
